--- a/instance/data-human.xlsx
+++ b/instance/data-human.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28350" windowHeight="12492"/>
+    <workbookView windowWidth="28470" windowHeight="12043"/>
   </bookViews>
   <sheets>
     <sheet name="Navigation" sheetId="1" r:id="rId1"/>
     <sheet name="Service" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Navigation!$A$1:$Q$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Navigation!$A$1:$Q$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="419">
   <si>
     <t>名称</t>
   </si>
@@ -105,6 +105,30 @@
     <t>•</t>
   </si>
   <si>
+    <t>Deepseek</t>
+  </si>
+  <si>
+    <t>Deepseek 开发平台</t>
+  </si>
+  <si>
+    <t>deepseek.png</t>
+  </si>
+  <si>
+    <t>https://platform.deepseek.com</t>
+  </si>
+  <si>
+    <t>Skills</t>
+  </si>
+  <si>
+    <t>开放 Agent Skills 平台</t>
+  </si>
+  <si>
+    <t>skills.png</t>
+  </si>
+  <si>
+    <t>https://skills.sh</t>
+  </si>
+  <si>
     <t>Docker Hub</t>
   </si>
   <si>
@@ -372,6 +396,18 @@
     <t>https://devenv.sh</t>
   </si>
   <si>
+    <t>Dify Wiki</t>
+  </si>
+  <si>
+    <t>Dify 官方手册</t>
+  </si>
+  <si>
+    <t>dify.png</t>
+  </si>
+  <si>
+    <t>https://legacy-docs.dify.ai/zh-hans</t>
+  </si>
+  <si>
     <t>Tailwindcss</t>
   </si>
   <si>
@@ -528,9 +564,6 @@
     <t>探索未至之境</t>
   </si>
   <si>
-    <t>deepseek.png</t>
-  </si>
-  <si>
     <t>https://chat.deepseek.com</t>
   </si>
   <si>
@@ -1131,9 +1164,6 @@
     <t>Agentic AI 管理后台</t>
   </si>
   <si>
-    <t>dify.png</t>
-  </si>
-  <si>
     <t>http://192.168.31.96:10080/apps</t>
   </si>
   <si>
@@ -1249,6 +1279,15 @@
   </si>
   <si>
     <t>https://github.com/Stirling-Tools/Stirling-PDF</t>
+  </si>
+  <si>
+    <t>* Open WebUI</t>
+  </si>
+  <si>
+    <t>自托管 AI 平台</t>
+  </si>
+  <si>
+    <t>openWebUI.png</t>
   </si>
 </sst>
 </file>
@@ -1675,7 +1714,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1775,15 +1814,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1911,7 +1941,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1923,34 +1953,34 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2035,7 +2065,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2105,9 +2135,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2116,9 +2143,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2437,7 +2461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
@@ -2639,8 +2663,8 @@
       <c r="J4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="12" t="s">
-        <v>23</v>
+      <c r="K4" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L4" s="11" t="s">
         <v>22</v>
@@ -2692,8 +2716,8 @@
       <c r="J5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="12" t="s">
-        <v>23</v>
+      <c r="K5" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L5" s="11" t="s">
         <v>22</v>
@@ -2715,16 +2739,16 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:17">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E6" s="13" t="s">
@@ -2768,16 +2792,16 @@
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:17">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E7" s="13" t="s">
@@ -2830,7 +2854,7 @@
       <c r="C8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="9" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="13" t="s">
@@ -2874,13 +2898,13 @@
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:17">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -2927,13 +2951,13 @@
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:17">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D10" s="9" t="s">
@@ -2980,16 +3004,16 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:17">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="9" t="s">
         <v>59</v>
       </c>
       <c r="E11" s="13" t="s">
@@ -3033,16 +3057,16 @@
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:17">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E12" s="13" t="s">
@@ -3051,8 +3075,8 @@
       <c r="F12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="12" t="s">
-        <v>23</v>
+      <c r="G12" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>22</v>
@@ -3060,29 +3084,29 @@
       <c r="I12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>23</v>
+      <c r="J12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q12" s="12" t="s">
-        <v>23</v>
+      <c r="N12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:17">
@@ -3113,11 +3137,11 @@
       <c r="I13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>22</v>
+      <c r="J13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L13" s="11" t="s">
         <v>22</v>
@@ -3128,8 +3152,8 @@
       <c r="N13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O13" s="11" t="s">
-        <v>22</v>
+      <c r="O13" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P13" s="11" t="s">
         <v>22</v>
@@ -3143,13 +3167,13 @@
         <v>68</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>21</v>
@@ -3157,8 +3181,8 @@
       <c r="F14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>22</v>
+      <c r="G14" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>22</v>
@@ -3172,37 +3196,37 @@
       <c r="K14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="11" t="s">
-        <v>22</v>
+      <c r="L14" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="11" t="s">
-        <v>22</v>
+      <c r="N14" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q14" s="17" t="s">
-        <v>22</v>
+      <c r="P14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>21</v>
@@ -3219,8 +3243,8 @@
       <c r="I15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="11" t="s">
-        <v>22</v>
+      <c r="J15" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>22</v>
@@ -3240,16 +3264,16 @@
       <c r="P15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q15" s="12" t="s">
-        <v>23</v>
+      <c r="Q15" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>77</v>
@@ -3260,41 +3284,41 @@
       <c r="E16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>23</v>
+      <c r="F16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="J16" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q16" s="12" t="s">
-        <v>23</v>
+      <c r="K16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:17">
@@ -3313,38 +3337,38 @@
       <c r="E17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>23</v>
+      <c r="F17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q17" s="12" t="s">
         <v>23</v>
@@ -3457,179 +3481,179 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:17">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:17">
+      <c r="A21" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="L20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="M20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="N20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="O20" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q20" s="22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" s="15" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A21" s="9" t="s">
+      <c r="B21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q21" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:17">
+      <c r="A22" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O22" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q22" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" s="15" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A23" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O21" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q21" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:17">
-      <c r="A22" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O22" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q22" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:17">
-      <c r="A23" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>106</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>22</v>
@@ -3676,13 +3700,13 @@
         <v>108</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
@@ -3723,19 +3747,19 @@
     </row>
     <row r="25" customHeight="1" spans="1:17">
       <c r="A25" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>22</v>
@@ -3776,19 +3800,19 @@
     </row>
     <row r="26" customHeight="1" spans="1:17">
       <c r="A26" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>22</v>
@@ -3805,8 +3829,8 @@
       <c r="J26" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="12" t="s">
-        <v>23</v>
+      <c r="K26" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L26" s="11" t="s">
         <v>22</v>
@@ -3817,8 +3841,8 @@
       <c r="N26" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O26" s="11" t="s">
-        <v>22</v>
+      <c r="O26" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P26" s="11" t="s">
         <v>22</v>
@@ -3828,20 +3852,20 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:17">
-      <c r="A27" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="A27" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="B27" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="C27" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>120</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>22</v>
@@ -3858,8 +3882,8 @@
       <c r="J27" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="12" t="s">
-        <v>23</v>
+      <c r="K27" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L27" s="11" t="s">
         <v>22</v>
@@ -3870,8 +3894,8 @@
       <c r="N27" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O27" s="11" t="s">
-        <v>22</v>
+      <c r="O27" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P27" s="11" t="s">
         <v>22</v>
@@ -3881,20 +3905,20 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:17">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="B28" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="C28" s="9" t="s">
         <v>123</v>
       </c>
+      <c r="D28" s="9" t="s">
+        <v>124</v>
+      </c>
       <c r="E28" s="10" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>22</v>
@@ -3911,8 +3935,8 @@
       <c r="J28" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K28" s="12" t="s">
-        <v>23</v>
+      <c r="K28" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L28" s="11" t="s">
         <v>22</v>
@@ -3923,8 +3947,8 @@
       <c r="N28" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O28" s="11" t="s">
-        <v>22</v>
+      <c r="O28" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P28" s="11" t="s">
         <v>22</v>
@@ -3934,20 +3958,20 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:17">
-      <c r="A29" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="A29" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="B29" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="C29" s="9" t="s">
         <v>127</v>
       </c>
+      <c r="D29" s="9" t="s">
+        <v>128</v>
+      </c>
       <c r="E29" s="10" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>22</v>
@@ -3964,8 +3988,8 @@
       <c r="J29" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K29" s="11" t="s">
-        <v>22</v>
+      <c r="K29" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L29" s="11" t="s">
         <v>22</v>
@@ -3976,11 +4000,11 @@
       <c r="N29" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O29" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P29" s="12" t="s">
-        <v>23</v>
+      <c r="O29" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q29" s="17" t="s">
         <v>22</v>
@@ -3988,43 +4012,43 @@
     </row>
     <row r="30" customHeight="1" spans="1:17">
       <c r="A30" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="2" t="s">
         <v>131</v>
       </c>
+      <c r="D30" s="9" t="s">
+        <v>132</v>
+      </c>
       <c r="E30" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>23</v>
+        <v>103</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I30" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>22</v>
+      <c r="H30" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L30" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M30" s="12" t="s">
-        <v>23</v>
+      <c r="M30" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="N30" s="11" t="s">
         <v>22</v>
@@ -4032,8 +4056,8 @@
       <c r="O30" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P30" s="12" t="s">
-        <v>23</v>
+      <c r="P30" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q30" s="17" t="s">
         <v>22</v>
@@ -4041,43 +4065,43 @@
     </row>
     <row r="31" customHeight="1" spans="1:17">
       <c r="A31" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="9" t="s">
         <v>135</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>23</v>
+        <v>103</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>23</v>
+      <c r="H31" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K31" s="11" t="s">
-        <v>22</v>
+      <c r="K31" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L31" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M31" s="12" t="s">
-        <v>23</v>
+      <c r="M31" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="N31" s="11" t="s">
         <v>22</v>
@@ -4100,25 +4124,25 @@
         <v>137</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="D32" s="9" t="s">
+        <v>139</v>
+      </c>
       <c r="E32" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>23</v>
+        <v>103</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>23</v>
+      <c r="H32" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>22</v>
@@ -4129,17 +4153,17 @@
       <c r="L32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M32" s="12" t="s">
-        <v>23</v>
+      <c r="M32" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="N32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O32" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P32" s="11" t="s">
-        <v>22</v>
+      <c r="O32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P32" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="Q32" s="17" t="s">
         <v>22</v>
@@ -4147,34 +4171,34 @@
     </row>
     <row r="33" customHeight="1" spans="1:17">
       <c r="A33" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D33" s="2" t="s">
         <v>142</v>
       </c>
+      <c r="D33" s="9" t="s">
+        <v>143</v>
+      </c>
       <c r="E33" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>22</v>
+        <v>103</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H33" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>22</v>
+      <c r="H33" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>22</v>
@@ -4182,17 +4206,17 @@
       <c r="L33" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M33" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N33" s="12" t="s">
-        <v>23</v>
+      <c r="M33" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O33" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P33" s="11" t="s">
-        <v>22</v>
+      <c r="P33" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="Q33" s="17" t="s">
         <v>22</v>
@@ -4200,31 +4224,31 @@
     </row>
     <row r="34" customHeight="1" spans="1:17">
       <c r="A34" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D34" s="2" t="s">
         <v>146</v>
       </c>
+      <c r="D34" s="9" t="s">
+        <v>147</v>
+      </c>
       <c r="E34" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>22</v>
+        <v>103</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>22</v>
+      <c r="H34" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>22</v>
@@ -4235,14 +4259,14 @@
       <c r="L34" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M34" s="11" t="s">
-        <v>22</v>
+      <c r="M34" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="N34" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O34" s="12" t="s">
-        <v>23</v>
+      <c r="O34" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="P34" s="11" t="s">
         <v>22</v>
@@ -4251,33 +4275,33 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" s="16" customFormat="1" customHeight="1" spans="1:17">
+    <row r="35" customHeight="1" spans="1:17">
       <c r="A35" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D35" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>150</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>22</v>
+        <v>103</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H35" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>22</v>
+      <c r="H35" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>22</v>
@@ -4288,129 +4312,129 @@
       <c r="L35" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="11" t="s">
-        <v>22</v>
+      <c r="M35" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="N35" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O35" s="12" t="s">
-        <v>23</v>
+      <c r="O35" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="P35" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q35" s="23" t="s">
-        <v>23</v>
+      <c r="Q35" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:17">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="E36" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="L36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="O36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q36" s="21" t="s">
-        <v>23</v>
+      <c r="E36" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q36" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:17">
       <c r="A37" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E37" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N37" s="12" t="s">
-        <v>23</v>
+      <c r="E37" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O37" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q37" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:17">
+      <c r="P37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q37" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" s="16" customFormat="1" customHeight="1" spans="1:17">
       <c r="A38" s="2" t="s">
         <v>159</v>
       </c>
@@ -4423,115 +4447,115 @@
       <c r="D38" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E38" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N38" s="12" t="s">
-        <v>23</v>
+      <c r="E38" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O38" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P38" s="12" t="s">
-        <v>23</v>
+      <c r="P38" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q38" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:17">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="E39" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q39" s="12" t="s">
+      <c r="E39" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P39" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q39" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:17">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" s="25" t="s">
-        <v>155</v>
-      </c>
       <c r="F40" s="12" t="s">
         <v>23</v>
       </c>
@@ -4570,232 +4594,232 @@
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:17">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E41" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N41" s="11" t="s">
-        <v>22</v>
+      <c r="E41" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O41" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q41" s="17" t="s">
-        <v>22</v>
+      <c r="P41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q41" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:17">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E42" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N42" s="11" t="s">
-        <v>22</v>
+      <c r="E42" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O42" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q42" s="17" t="s">
-        <v>22</v>
+      <c r="P42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:17">
       <c r="A43" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="C43" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="D43" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="E43" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N43" s="11" t="s">
-        <v>22</v>
+      <c r="E43" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O43" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q43" s="17" t="s">
-        <v>22</v>
+      <c r="P43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q43" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:17">
       <c r="A44" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="C44" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="D44" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="E44" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O44" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q44" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:17">
+      <c r="A45" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E44" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O44" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q44" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:17">
-      <c r="A45" s="9" t="s">
+      <c r="B45" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="C45" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="D45" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="E45" s="25" t="s">
-        <v>155</v>
+      <c r="E45" s="24" t="s">
+        <v>167</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>22</v>
@@ -4836,72 +4860,72 @@
     </row>
     <row r="46" customHeight="1" spans="1:17">
       <c r="A46" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B46" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="C46" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="D46" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="E46" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O46" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q46" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:17">
+      <c r="A47" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="E46" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O46" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q46" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:17">
-      <c r="A47" s="2" t="s">
+      <c r="B47" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E47" s="25" t="s">
-        <v>155</v>
+      <c r="E47" s="24" t="s">
+        <v>167</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>22</v>
@@ -4918,8 +4942,8 @@
       <c r="J47" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K47" s="12" t="s">
-        <v>23</v>
+      <c r="K47" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L47" s="11" t="s">
         <v>22</v>
@@ -4942,25 +4966,25 @@
     </row>
     <row r="48" customHeight="1" spans="1:17">
       <c r="A48" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B48" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="C48" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="D48" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E48" s="25" t="s">
-        <v>155</v>
+      <c r="E48" s="24" t="s">
+        <v>167</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G48" s="12" t="s">
-        <v>23</v>
+      <c r="G48" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H48" s="11" t="s">
         <v>22</v>
@@ -4968,8 +4992,8 @@
       <c r="I48" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J48" s="12" t="s">
-        <v>23</v>
+      <c r="J48" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>22</v>
@@ -4983,37 +5007,37 @@
       <c r="N48" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q48" s="12" t="s">
-        <v>23</v>
+      <c r="O48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q48" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:17">
       <c r="A49" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B49" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="C49" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="D49" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>155</v>
+      <c r="E49" s="24" t="s">
+        <v>167</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G49" s="12" t="s">
-        <v>23</v>
+      <c r="G49" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H49" s="11" t="s">
         <v>22</v>
@@ -5021,8 +5045,8 @@
       <c r="I49" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J49" s="12" t="s">
-        <v>23</v>
+      <c r="J49" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>22</v>
@@ -5036,143 +5060,143 @@
       <c r="N49" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q49" s="12" t="s">
-        <v>23</v>
+      <c r="O49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q49" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:17">
       <c r="A50" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q50" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:17">
+      <c r="A51" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="E50" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q50" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="1:17">
-      <c r="A51" s="2" t="s">
+      <c r="B51" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N51" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O51" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q51" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:17">
+      <c r="A52" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="E51" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q51" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="1:17">
-      <c r="A52" s="2" t="s">
+      <c r="B52" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E52" s="25" t="s">
-        <v>155</v>
+      <c r="E52" s="24" t="s">
+        <v>167</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G52" s="11" t="s">
-        <v>22</v>
+      <c r="G52" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H52" s="11" t="s">
         <v>22</v>
@@ -5198,28 +5222,28 @@
       <c r="O52" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q52" s="17" t="s">
-        <v>22</v>
+      <c r="P52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q52" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:17">
       <c r="A53" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B53" s="26" t="s">
+      <c r="C53" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E53" s="25" t="s">
-        <v>155</v>
+      <c r="E53" s="24" t="s">
+        <v>167</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>22</v>
@@ -5260,343 +5284,343 @@
     </row>
     <row r="54" customHeight="1" spans="1:17">
       <c r="A54" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q54" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:17">
+      <c r="A55" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E54" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q54" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" s="16" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A55" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J55" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q55" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:17">
+      <c r="A56" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E55" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q55" s="27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="1:17">
-      <c r="A56" s="15" t="s">
+      <c r="B56" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="C56" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C56" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E56" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I56" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J56" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="K56" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="L56" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="M56" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N56" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="O56" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="P56" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q56" s="22" t="s">
+      <c r="E56" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q56" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:17">
       <c r="A57" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q57" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" s="16" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A58" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E57" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L57" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N57" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P57" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q57" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="1:17">
-      <c r="A58" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="E58" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q58" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:17">
+      <c r="A59" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="E58" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G58" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L58" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q58" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="1:17">
-      <c r="A59" s="2" t="s">
+      <c r="B59" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="E59" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E59" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P59" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q59" s="12" t="s">
-        <v>23</v>
+      <c r="F59" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L59" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M59" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O59" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="P59" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q59" s="22" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:17">
       <c r="A60" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E60" s="29" t="s">
-        <v>234</v>
+      <c r="E60" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G60" s="11" t="s">
-        <v>22</v>
+      <c r="G60" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>22</v>
@@ -5610,14 +5634,14 @@
       <c r="K60" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L60" s="11" t="s">
-        <v>22</v>
+      <c r="L60" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="M60" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N60" s="11" t="s">
-        <v>22</v>
+      <c r="N60" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O60" s="11" t="s">
         <v>22</v>
@@ -5631,10 +5655,10 @@
     </row>
     <row r="61" customHeight="1" spans="1:17">
       <c r="A61" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>252</v>
@@ -5642,14 +5666,14 @@
       <c r="D61" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E61" s="29" t="s">
-        <v>234</v>
+      <c r="E61" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="11" t="s">
-        <v>22</v>
+      <c r="G61" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>22</v>
@@ -5657,14 +5681,14 @@
       <c r="I61" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J61" s="12" t="s">
-        <v>23</v>
+      <c r="J61" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L61" s="11" t="s">
-        <v>22</v>
+      <c r="L61" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="M61" s="11" t="s">
         <v>22</v>
@@ -5675,8 +5699,8 @@
       <c r="O61" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P61" s="12" t="s">
-        <v>23</v>
+      <c r="P61" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q61" s="12" t="s">
         <v>23</v>
@@ -5687,16 +5711,16 @@
         <v>254</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E62" s="29" t="s">
-        <v>234</v>
+        <v>257</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>22</v>
@@ -5737,19 +5761,19 @@
     </row>
     <row r="63" customHeight="1" spans="1:17">
       <c r="A63" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E63" s="29" t="s">
-        <v>234</v>
+        <v>261</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>22</v>
@@ -5766,8 +5790,8 @@
       <c r="J63" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K63" s="12" t="s">
-        <v>23</v>
+      <c r="K63" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L63" s="11" t="s">
         <v>22</v>
@@ -5781,28 +5805,28 @@
       <c r="O63" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P63" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q63" s="17" t="s">
-        <v>22</v>
+      <c r="P63" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q63" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:17">
       <c r="A64" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E64" s="29" t="s">
-        <v>234</v>
+        <v>264</v>
+      </c>
+      <c r="E64" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>22</v>
@@ -5819,8 +5843,8 @@
       <c r="J64" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K64" s="12" t="s">
-        <v>23</v>
+      <c r="K64" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L64" s="11" t="s">
         <v>22</v>
@@ -5834,28 +5858,28 @@
       <c r="O64" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P64" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q64" s="17" t="s">
-        <v>22</v>
+      <c r="P64" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q64" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:17">
       <c r="A65" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E65" s="29" t="s">
-        <v>234</v>
+        <v>261</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>22</v>
@@ -5872,8 +5896,8 @@
       <c r="J65" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K65" s="12" t="s">
-        <v>23</v>
+      <c r="K65" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L65" s="11" t="s">
         <v>22</v>
@@ -5887,11 +5911,11 @@
       <c r="O65" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P65" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q65" s="17" t="s">
-        <v>22</v>
+      <c r="P65" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q65" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:17">
@@ -5907,8 +5931,8 @@
       <c r="D66" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E66" s="29" t="s">
-        <v>234</v>
+      <c r="E66" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>22</v>
@@ -5952,16 +5976,16 @@
         <v>271</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="D67" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E67" s="29" t="s">
-        <v>234</v>
+      <c r="E67" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>22</v>
@@ -6002,19 +6026,19 @@
     </row>
     <row r="68" customHeight="1" spans="1:17">
       <c r="A68" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E68" s="29" t="s">
-        <v>234</v>
+      <c r="E68" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>22</v>
@@ -6031,8 +6055,8 @@
       <c r="J68" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K68" s="11" t="s">
-        <v>22</v>
+      <c r="K68" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L68" s="11" t="s">
         <v>22</v>
@@ -6055,19 +6079,19 @@
     </row>
     <row r="69" customHeight="1" spans="1:17">
       <c r="A69" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E69" s="29" t="s">
-        <v>234</v>
+      <c r="E69" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>22</v>
@@ -6084,8 +6108,8 @@
       <c r="J69" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K69" s="11" t="s">
-        <v>22</v>
+      <c r="K69" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L69" s="11" t="s">
         <v>22</v>
@@ -6108,19 +6132,19 @@
     </row>
     <row r="70" customHeight="1" spans="1:17">
       <c r="A70" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E70" s="29" t="s">
-        <v>234</v>
+      <c r="E70" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>22</v>
@@ -6137,8 +6161,8 @@
       <c r="J70" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K70" s="11" t="s">
-        <v>22</v>
+      <c r="K70" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L70" s="11" t="s">
         <v>22</v>
@@ -6161,19 +6185,19 @@
     </row>
     <row r="71" customHeight="1" spans="1:17">
       <c r="A71" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E71" s="29" t="s">
-        <v>234</v>
+      <c r="E71" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>22</v>
@@ -6225,8 +6249,8 @@
       <c r="D72" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E72" s="29" t="s">
-        <v>234</v>
+      <c r="E72" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>22</v>
@@ -6258,11 +6282,11 @@
       <c r="O72" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P72" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q72" s="12" t="s">
-        <v>23</v>
+      <c r="P72" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q72" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:17">
@@ -6278,8 +6302,8 @@
       <c r="D73" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E73" s="29" t="s">
-        <v>234</v>
+      <c r="E73" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>22</v>
@@ -6326,13 +6350,13 @@
         <v>299</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E74" s="29" t="s">
-        <v>234</v>
+      <c r="E74" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>22</v>
@@ -6367,25 +6391,25 @@
       <c r="P74" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q74" s="11" t="s">
+      <c r="Q74" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:17">
       <c r="A75" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E75" s="29" t="s">
-        <v>234</v>
+      <c r="E75" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>22</v>
@@ -6417,28 +6441,28 @@
       <c r="O75" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P75" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q75" s="11" t="s">
-        <v>22</v>
+      <c r="P75" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q75" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:17">
       <c r="A76" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E76" s="29" t="s">
-        <v>234</v>
+      <c r="E76" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>22</v>
@@ -6452,8 +6476,8 @@
       <c r="I76" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J76" s="11" t="s">
-        <v>22</v>
+      <c r="J76" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K76" s="11" t="s">
         <v>22</v>
@@ -6470,8 +6494,8 @@
       <c r="O76" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P76" s="12" t="s">
-        <v>23</v>
+      <c r="P76" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q76" s="17" t="s">
         <v>22</v>
@@ -6479,19 +6503,19 @@
     </row>
     <row r="77" customHeight="1" spans="1:17">
       <c r="A77" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E77" s="29" t="s">
-        <v>234</v>
+      <c r="E77" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>22</v>
@@ -6505,8 +6529,8 @@
       <c r="I77" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J77" s="11" t="s">
-        <v>22</v>
+      <c r="J77" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K77" s="11" t="s">
         <v>22</v>
@@ -6517,8 +6541,8 @@
       <c r="M77" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N77" s="12" t="s">
-        <v>23</v>
+      <c r="N77" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O77" s="11" t="s">
         <v>22</v>
@@ -6526,69 +6550,233 @@
       <c r="P77" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q77" s="17" t="s">
+      <c r="Q77" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:17">
       <c r="A78" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="E78" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q78" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:17">
+      <c r="A79" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="E78" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="F78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N78" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q78" s="17" t="s">
+      <c r="B79" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E79" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O79" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P79" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q79" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:17">
+      <c r="A80" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E80" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N80" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P80" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q80" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:17">
+      <c r="A81" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N81" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q81" s="17" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D28" r:id="rId1" display="https://legacy-docs.dify.ai/zh-hans"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://platform.deepseek.com"/>
+    <hyperlink ref="D4" r:id="rId3" display="https://skills.sh" tooltip="https://skills.sh"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="33" orientation="portrait"/>
   <headerFooter/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="89" max="16" man="1"/>
+    <brk id="92" max="16" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="5" max="1048575" man="1"/>
@@ -6599,7 +6787,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" style="2" customWidth="1"/>
@@ -6668,19 +6856,19 @@
     </row>
     <row r="2" customHeight="1" spans="1:17">
       <c r="A2" s="9" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>22</v>
@@ -6721,19 +6909,19 @@
     </row>
     <row r="3" customHeight="1" spans="1:17">
       <c r="A3" s="9" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>22</v>
@@ -6774,19 +6962,19 @@
     </row>
     <row r="4" customHeight="1" spans="1:17">
       <c r="A4" s="9" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D4" s="9">
         <v>2</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>22</v>
@@ -6827,19 +7015,19 @@
     </row>
     <row r="5" customHeight="1" spans="1:17">
       <c r="A5" s="9" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D5" s="9">
         <v>3</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>22</v>
@@ -6880,19 +7068,19 @@
     </row>
     <row r="6" customHeight="1" spans="1:17">
       <c r="A6" s="9" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D6" s="9">
         <v>4</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>22</v>
@@ -6933,19 +7121,19 @@
     </row>
     <row r="7" customHeight="1" spans="1:17">
       <c r="A7" s="9" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D7" s="9">
         <v>5</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>22</v>
@@ -6986,19 +7174,19 @@
     </row>
     <row r="8" customHeight="1" spans="1:17">
       <c r="A8" s="9" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D8" s="9">
         <v>6</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>22</v>
@@ -7039,19 +7227,19 @@
     </row>
     <row r="9" customHeight="1" spans="1:17">
       <c r="A9" s="9" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D9" s="9">
         <v>7</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>22</v>
@@ -7092,19 +7280,19 @@
     </row>
     <row r="10" customHeight="1" spans="1:17">
       <c r="A10" s="9" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D10" s="9">
         <v>8</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>22</v>
@@ -7145,19 +7333,19 @@
     </row>
     <row r="11" customHeight="1" spans="1:17">
       <c r="A11" s="9" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D11" s="9">
         <v>9</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>22</v>
@@ -7198,19 +7386,19 @@
     </row>
     <row r="12" customHeight="1" spans="1:17">
       <c r="A12" s="9" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D12" s="9">
         <v>10</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>22</v>
@@ -7251,19 +7439,19 @@
     </row>
     <row r="13" customHeight="1" spans="1:17">
       <c r="A13" s="9" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="D13" s="9">
         <v>11</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>22</v>
@@ -7304,19 +7492,19 @@
     </row>
     <row r="14" customHeight="1" spans="1:17">
       <c r="A14" s="9" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>22</v>
@@ -7357,19 +7545,19 @@
     </row>
     <row r="15" customHeight="1" spans="1:17">
       <c r="A15" s="9" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>22</v>
@@ -7410,19 +7598,19 @@
     </row>
     <row r="16" customHeight="1" spans="1:17">
       <c r="A16" s="9" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
@@ -7463,19 +7651,19 @@
     </row>
     <row r="17" customHeight="1" spans="1:17">
       <c r="A17" s="9" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>355</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>344</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>22</v>
@@ -7516,19 +7704,19 @@
     </row>
     <row r="18" customHeight="1" spans="1:17">
       <c r="A18" s="9" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>22</v>
@@ -7569,19 +7757,19 @@
     </row>
     <row r="19" customHeight="1" spans="1:17">
       <c r="A19" s="9" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>22</v>
@@ -7622,19 +7810,19 @@
     </row>
     <row r="20" customHeight="1" spans="1:17">
       <c r="A20" s="9" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>366</v>
+        <v>123</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>22</v>
@@ -7675,19 +7863,19 @@
     </row>
     <row r="21" customHeight="1" spans="1:17">
       <c r="A21" s="2" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="D21" s="2">
         <v>13</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>22</v>
@@ -7728,19 +7916,19 @@
     </row>
     <row r="22" customHeight="1" spans="1:17">
       <c r="A22" s="9" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>22</v>
@@ -7781,19 +7969,19 @@
     </row>
     <row r="23" customHeight="1" spans="1:17">
       <c r="A23" s="2" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>22</v>
@@ -7834,19 +8022,19 @@
     </row>
     <row r="24" customHeight="1" spans="1:17">
       <c r="A24" s="2" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
@@ -7887,19 +8075,19 @@
     </row>
     <row r="25" customHeight="1" spans="1:17">
       <c r="A25" s="2" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>23</v>
@@ -7940,19 +8128,19 @@
     </row>
     <row r="26" customHeight="1" spans="1:17">
       <c r="A26" s="9" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="D26" s="9">
         <v>15</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>23</v>
@@ -7993,19 +8181,19 @@
     </row>
     <row r="27" customHeight="1" spans="1:17">
       <c r="A27" s="9" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>23</v>
@@ -8046,19 +8234,19 @@
     </row>
     <row r="28" customHeight="1" spans="1:17">
       <c r="A28" s="9" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>23</v>
@@ -8099,19 +8287,19 @@
     </row>
     <row r="29" customHeight="1" spans="1:17">
       <c r="A29" s="9" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>23</v>
@@ -8152,19 +8340,19 @@
     </row>
     <row r="30" customHeight="1" spans="1:17">
       <c r="A30" s="9" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>23</v>
@@ -8200,6 +8388,59 @@
         <v>23</v>
       </c>
       <c r="Q30" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:17">
+      <c r="A31" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D31" s="9">
+        <v>12</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q31" s="12" t="s">
         <v>23</v>
       </c>
     </row>

--- a/instance/data-human.xlsx
+++ b/instance/data-human.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Service" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Navigation!$A$1:$Q$100</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Navigation!$A$1:$Q$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="457">
   <si>
     <t>名称</t>
   </si>
@@ -378,6 +378,15 @@
     <t>https://resource.tp-link.com.cn</t>
   </si>
   <si>
+    <t>Nix Dev</t>
+  </si>
+  <si>
+    <t>Nix 生态系统官方文档</t>
+  </si>
+  <si>
+    <t>https://nix.dev</t>
+  </si>
+  <si>
     <t>NixOS Manual</t>
   </si>
   <si>
@@ -396,6 +405,30 @@
     <t>https://devenv.sh</t>
   </si>
   <si>
+    <t>Terminaltrove</t>
+  </si>
+  <si>
+    <t>终端应用数据库</t>
+  </si>
+  <si>
+    <t>terminalTrove.png</t>
+  </si>
+  <si>
+    <t>https://terminaltrove.com</t>
+  </si>
+  <si>
+    <t>TLDR</t>
+  </si>
+  <si>
+    <t>社区驱动的 man 页</t>
+  </si>
+  <si>
+    <t>tldr.png</t>
+  </si>
+  <si>
+    <t>https://tldr.sh</t>
+  </si>
+  <si>
     <t>Dify Wiki</t>
   </si>
   <si>
@@ -441,6 +474,39 @@
     <t>https://reka-ui.com/docs/components/autocomplete</t>
   </si>
   <si>
+    <t>UI Verse</t>
+  </si>
+  <si>
+    <t>uiverse.png</t>
+  </si>
+  <si>
+    <t>https://uiverse.io</t>
+  </si>
+  <si>
+    <t>Inspira UI</t>
+  </si>
+  <si>
+    <t>UI 动画组件库</t>
+  </si>
+  <si>
+    <t>inspiraUI.png</t>
+  </si>
+  <si>
+    <t>https://inspira-ui.com/docs/cn</t>
+  </si>
+  <si>
+    <t>Patterns</t>
+  </si>
+  <si>
+    <t>前端架构手册</t>
+  </si>
+  <si>
+    <t>patterns.png</t>
+  </si>
+  <si>
+    <t>https://www.patterns.dev</t>
+  </si>
+  <si>
     <t>Ifixit</t>
   </si>
   <si>
@@ -486,6 +552,30 @@
     <t>https://www.gov.cn/index.htm</t>
   </si>
   <si>
+    <t>国家统计局</t>
+  </si>
+  <si>
+    <t>国家数据统计</t>
+  </si>
+  <si>
+    <t>https://www.stats.gov.cn</t>
+  </si>
+  <si>
+    <t>全国标准信息公共服务平台</t>
+  </si>
+  <si>
+    <t>国家标准文件手册</t>
+  </si>
+  <si>
+    <t>https://std.samr.gov.cn</t>
+  </si>
+  <si>
+    <t>国家标准全文公开</t>
+  </si>
+  <si>
+    <t>https://openstd.samr.gov.cn/bzgk/gb/index</t>
+  </si>
+  <si>
     <t>Blender</t>
   </si>
   <si>
@@ -498,18 +588,6 @@
     <t>https://opendata.blender.org</t>
   </si>
   <si>
-    <t>Terminaltrove</t>
-  </si>
-  <si>
-    <t>终端应用数据库</t>
-  </si>
-  <si>
-    <t>terminalTrove.png</t>
-  </si>
-  <si>
-    <t>https://terminaltrove.com</t>
-  </si>
-  <si>
     <t>屏库</t>
   </si>
   <si>
@@ -651,6 +729,18 @@
     <t>https://patorjk.com/software/taag</t>
   </si>
   <si>
+    <t>CHALK</t>
+  </si>
+  <si>
+    <t>代码截图生成器</t>
+  </si>
+  <si>
+    <t>chalk.png</t>
+  </si>
+  <si>
+    <t>https://chalk.ist</t>
+  </si>
+  <si>
     <t>Easings</t>
   </si>
   <si>
@@ -663,6 +753,18 @@
     <t>https://easings.net/zh-cn</t>
   </si>
   <si>
+    <t>Color Review</t>
+  </si>
+  <si>
+    <t>颜色可读性检查</t>
+  </si>
+  <si>
+    <t>colorReview.png</t>
+  </si>
+  <si>
+    <t>https://color.review</t>
+  </si>
+  <si>
     <t>即梦</t>
   </si>
   <si>
@@ -709,6 +811,18 @@
   </si>
   <si>
     <t>https://www.chinavid.com/color.html</t>
+  </si>
+  <si>
+    <t>Color Adobe</t>
+  </si>
+  <si>
+    <t>Adobe 色彩生成方案</t>
+  </si>
+  <si>
+    <t>adobe.png</t>
+  </si>
+  <si>
+    <t>https://color.adobe.com/zh</t>
   </si>
   <si>
     <t>Blobmaker</t>
@@ -2461,13 +2575,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="24.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="54.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="49.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.125" style="3" customWidth="1"/>
     <col min="6" max="17" width="8.625" style="4" customWidth="1"/>
     <col min="18" max="16384" width="9" style="2"/>
@@ -3912,10 +4026,10 @@
         <v>122</v>
       </c>
       <c r="C28" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>103</v>
@@ -3958,17 +4072,17 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:17">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="C29" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="D29" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>103</v>
@@ -3988,8 +4102,8 @@
       <c r="J29" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K29" s="12" t="s">
-        <v>23</v>
+      <c r="K29" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L29" s="11" t="s">
         <v>22</v>
@@ -4000,8 +4114,8 @@
       <c r="N29" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O29" s="11" t="s">
-        <v>22</v>
+      <c r="O29" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P29" s="11" t="s">
         <v>22</v>
@@ -4011,17 +4125,17 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:17">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>132</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>103</v>
@@ -4041,8 +4155,8 @@
       <c r="J30" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="12" t="s">
-        <v>23</v>
+      <c r="K30" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L30" s="11" t="s">
         <v>22</v>
@@ -4053,8 +4167,8 @@
       <c r="N30" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O30" s="11" t="s">
-        <v>22</v>
+      <c r="O30" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P30" s="11" t="s">
         <v>22</v>
@@ -4064,13 +4178,13 @@
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:17">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="9" t="s">
         <v>134</v>
       </c>
       <c r="D31" s="9" t="s">
@@ -4094,8 +4208,8 @@
       <c r="J31" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K31" s="12" t="s">
-        <v>23</v>
+      <c r="K31" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L31" s="11" t="s">
         <v>22</v>
@@ -4106,8 +4220,8 @@
       <c r="N31" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O31" s="11" t="s">
-        <v>22</v>
+      <c r="O31" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P31" s="11" t="s">
         <v>22</v>
@@ -4117,13 +4231,13 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:17">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="9" t="s">
         <v>138</v>
       </c>
       <c r="D32" s="9" t="s">
@@ -4147,8 +4261,8 @@
       <c r="J32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K32" s="11" t="s">
-        <v>22</v>
+      <c r="K32" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L32" s="11" t="s">
         <v>22</v>
@@ -4159,11 +4273,11 @@
       <c r="N32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O32" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P32" s="12" t="s">
-        <v>23</v>
+      <c r="O32" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q32" s="17" t="s">
         <v>22</v>
@@ -4185,29 +4299,29 @@
       <c r="E33" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F33" s="12" t="s">
-        <v>23</v>
+      <c r="F33" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H33" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>22</v>
+      <c r="H33" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L33" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M33" s="12" t="s">
-        <v>23</v>
+      <c r="M33" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="N33" s="11" t="s">
         <v>22</v>
@@ -4215,8 +4329,8 @@
       <c r="O33" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P33" s="12" t="s">
-        <v>23</v>
+      <c r="P33" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q33" s="17" t="s">
         <v>22</v>
@@ -4227,40 +4341,40 @@
         <v>144</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="9" t="s">
         <v>146</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>147</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F34" s="12" t="s">
-        <v>23</v>
+      <c r="F34" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H34" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>23</v>
+      <c r="H34" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="11" t="s">
-        <v>22</v>
+      <c r="K34" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L34" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M34" s="12" t="s">
-        <v>23</v>
+      <c r="M34" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="N34" s="11" t="s">
         <v>22</v>
@@ -4277,43 +4391,43 @@
     </row>
     <row r="35" customHeight="1" spans="1:17">
       <c r="A35" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="D35" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F35" s="12" t="s">
-        <v>23</v>
+      <c r="F35" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H35" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>23</v>
+      <c r="H35" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="11" t="s">
-        <v>22</v>
+      <c r="K35" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L35" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="12" t="s">
-        <v>23</v>
+      <c r="M35" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="N35" s="11" t="s">
         <v>22</v>
@@ -4330,16 +4444,16 @@
     </row>
     <row r="36" customHeight="1" spans="1:17">
       <c r="A36" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>103</v>
@@ -4359,8 +4473,8 @@
       <c r="J36" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="11" t="s">
-        <v>22</v>
+      <c r="K36" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L36" s="11" t="s">
         <v>22</v>
@@ -4368,8 +4482,8 @@
       <c r="M36" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N36" s="12" t="s">
-        <v>23</v>
+      <c r="N36" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O36" s="11" t="s">
         <v>22</v>
@@ -4383,16 +4497,16 @@
     </row>
     <row r="37" customHeight="1" spans="1:17">
       <c r="A37" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>103</v>
@@ -4412,8 +4526,8 @@
       <c r="J37" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="11" t="s">
-        <v>22</v>
+      <c r="K37" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L37" s="11" t="s">
         <v>22</v>
@@ -4424,8 +4538,8 @@
       <c r="N37" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O37" s="12" t="s">
-        <v>23</v>
+      <c r="O37" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="P37" s="11" t="s">
         <v>22</v>
@@ -4434,18 +4548,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" s="16" customFormat="1" customHeight="1" spans="1:17">
+    <row r="38" customHeight="1" spans="1:17">
       <c r="A38" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>103</v>
@@ -4480,87 +4594,87 @@
       <c r="O38" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P38" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q38" s="12" t="s">
-        <v>23</v>
+      <c r="P38" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:17">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="C39" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="D39" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D39" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="K39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="M39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P39" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q39" s="21" t="s">
-        <v>23</v>
+      <c r="E39" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P39" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q39" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:17">
       <c r="A40" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="D40" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>167</v>
+      <c r="E40" s="10" t="s">
+        <v>103</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G40" s="12" t="s">
-        <v>23</v>
+      <c r="G40" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>23</v>
@@ -4568,217 +4682,217 @@
       <c r="I40" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J40" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K40" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L40" s="12" t="s">
-        <v>23</v>
+      <c r="J40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="M40" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="N40" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O40" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P40" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q40" s="12" t="s">
-        <v>23</v>
+      <c r="N40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q40" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:17">
       <c r="A41" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="E41" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q41" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:17">
+      <c r="A42" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="B42" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E41" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q41" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:17">
-      <c r="A42" s="9" t="s">
+      <c r="C42" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="E42" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q42" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:17">
+      <c r="A43" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D42" s="9" t="s">
+      <c r="B43" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E42" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P42" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q42" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:17">
-      <c r="A43" s="9" t="s">
+      <c r="C43" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="E43" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N43" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O43" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P43" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q43" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:17">
+      <c r="A44" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="B44" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="E43" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q43" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="1:17">
-      <c r="A44" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="E44" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>22</v>
+      <c r="E44" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>22</v>
+      <c r="H44" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>22</v>
@@ -4789,14 +4903,14 @@
       <c r="L44" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M44" s="11" t="s">
-        <v>22</v>
+      <c r="M44" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="N44" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O44" s="12" t="s">
-        <v>23</v>
+      <c r="O44" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="P44" s="11" t="s">
         <v>22</v>
@@ -4807,367 +4921,367 @@
     </row>
     <row r="45" customHeight="1" spans="1:17">
       <c r="A45" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q45" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" s="16" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A46" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E46" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O46" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q46" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:17">
+      <c r="A47" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E45" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O45" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q45" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:17">
-      <c r="A46" s="9" t="s">
+      <c r="B47" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="C47" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="D47" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="E47" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="E46" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O46" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q46" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:17">
-      <c r="A47" s="9" t="s">
+      <c r="F47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P47" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q47" s="21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:17">
+      <c r="A48" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B48" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C48" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="E48" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q48" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:17">
+      <c r="A49" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E47" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O47" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q47" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="1:17">
-      <c r="A48" s="9" t="s">
+      <c r="B49" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="C49" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="D49" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="E49" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q49" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:17">
+      <c r="A50" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E48" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q48" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="1:17">
-      <c r="A49" s="9" t="s">
+      <c r="B50" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="C50" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="E49" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q49" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="1:17">
-      <c r="A50" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="E50" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>22</v>
+        <v>193</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K50" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N50" s="11" t="s">
-        <v>22</v>
+      <c r="L50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q50" s="17" t="s">
-        <v>22</v>
+      <c r="P50" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q50" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:17">
       <c r="A51" s="9" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>22</v>
+        <v>193</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>22</v>
+      <c r="H51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O51" s="11" t="s">
-        <v>22</v>
+      <c r="K51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O51" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P51" s="12" t="s">
         <v>23</v>
@@ -5178,25 +5292,25 @@
     </row>
     <row r="52" customHeight="1" spans="1:17">
       <c r="A52" s="9" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G52" s="12" t="s">
-        <v>23</v>
+      <c r="G52" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H52" s="11" t="s">
         <v>22</v>
@@ -5204,8 +5318,8 @@
       <c r="I52" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J52" s="12" t="s">
-        <v>23</v>
+      <c r="J52" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>22</v>
@@ -5219,514 +5333,514 @@
       <c r="N52" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P52" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q52" s="12" t="s">
-        <v>23</v>
+      <c r="O52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P52" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q52" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:17">
       <c r="A53" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q53" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:17">
+      <c r="A54" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C54" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="D54" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="E54" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q54" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:17">
+      <c r="A55" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="B55" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="E53" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q53" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="1:17">
-      <c r="A54" s="2" t="s">
+      <c r="C55" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="D55" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="E55" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O55" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q55" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:17">
+      <c r="A56" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="B56" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="E54" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q54" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="1:17">
-      <c r="A55" s="2" t="s">
+      <c r="C56" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="D56" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="E56" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O56" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q56" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:17">
+      <c r="A57" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="B57" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="E55" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q55" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="1:17">
-      <c r="A56" s="2" t="s">
+      <c r="C57" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="B56" s="25" t="s">
+      <c r="D57" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="E57" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O57" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P57" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q57" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:17">
+      <c r="A58" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="B58" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="E56" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q56" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="1:17">
-      <c r="A57" s="2" t="s">
+      <c r="C58" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="D58" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="E58" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K58" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O58" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q58" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:17">
+      <c r="A59" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E57" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q57" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" s="16" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E58" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q58" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="1:17">
-      <c r="A59" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="E59" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="F59" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G59" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J59" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="K59" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="L59" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="M59" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N59" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="O59" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="P59" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q59" s="22" t="s">
+      <c r="E59" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q59" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:17">
       <c r="A60" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E60" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K60" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q60" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:17">
+      <c r="A61" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C61" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="D61" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="E61" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P61" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q61" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:17">
+      <c r="A62" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="B62" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="E60" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G60" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I60" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J60" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K60" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L60" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M60" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N60" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O60" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P60" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q60" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="1:17">
-      <c r="A61" s="2" t="s">
+      <c r="C62" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="D62" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E61" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L61" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q61" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="1:17">
-      <c r="A62" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E62" s="27" t="s">
-        <v>245</v>
+      <c r="E62" s="24" t="s">
+        <v>193</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G62" s="11" t="s">
-        <v>22</v>
+      <c r="G62" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H62" s="11" t="s">
         <v>22</v>
@@ -5761,19 +5875,19 @@
     </row>
     <row r="63" customHeight="1" spans="1:17">
       <c r="A63" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E63" s="27" t="s">
-        <v>245</v>
+        <v>255</v>
+      </c>
+      <c r="E63" s="24" t="s">
+        <v>193</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>22</v>
@@ -5805,28 +5919,28 @@
       <c r="O63" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P63" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q63" s="12" t="s">
-        <v>23</v>
+      <c r="P63" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q63" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:17">
       <c r="A64" s="2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>245</v>
+      <c r="E64" s="24" t="s">
+        <v>193</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>22</v>
@@ -5858,28 +5972,28 @@
       <c r="O64" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P64" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q64" s="12" t="s">
-        <v>23</v>
+      <c r="P64" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q64" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:17">
       <c r="A65" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E65" s="27" t="s">
-        <v>245</v>
+        <v>263</v>
+      </c>
+      <c r="E65" s="24" t="s">
+        <v>193</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>22</v>
@@ -5911,28 +6025,28 @@
       <c r="O65" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P65" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q65" s="12" t="s">
-        <v>23</v>
+      <c r="P65" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q65" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:17">
       <c r="A66" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E66" s="27" t="s">
-        <v>245</v>
+      <c r="E66" s="24" t="s">
+        <v>193</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>22</v>
@@ -5949,8 +6063,8 @@
       <c r="J66" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K66" s="12" t="s">
-        <v>23</v>
+      <c r="K66" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L66" s="11" t="s">
         <v>22</v>
@@ -5973,19 +6087,19 @@
     </row>
     <row r="67" customHeight="1" spans="1:17">
       <c r="A67" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E67" s="27" t="s">
-        <v>245</v>
+      <c r="E67" s="24" t="s">
+        <v>193</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>22</v>
@@ -6002,8 +6116,8 @@
       <c r="J67" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K67" s="12" t="s">
-        <v>23</v>
+      <c r="K67" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L67" s="11" t="s">
         <v>22</v>
@@ -6026,184 +6140,184 @@
     </row>
     <row r="68" customHeight="1" spans="1:17">
       <c r="A68" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="E68" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J68" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q68" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" s="16" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A69" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E68" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J68" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K68" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q68" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:17">
-      <c r="A69" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="E69" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q69" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:17">
+      <c r="A70" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="B70" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="E69" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J69" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K69" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q69" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:17">
-      <c r="A70" s="2" t="s">
+      <c r="C70" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D70" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="E70" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E70" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J70" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K70" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P70" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q70" s="17" t="s">
+      <c r="F70" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J70" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K70" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L70" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M70" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N70" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O70" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="P70" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q70" s="22" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:17">
       <c r="A71" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>289</v>
-      </c>
       <c r="E71" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G71" s="11" t="s">
-        <v>22</v>
+      <c r="G71" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H71" s="11" t="s">
         <v>22</v>
@@ -6217,46 +6331,46 @@
       <c r="K71" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L71" s="11" t="s">
-        <v>22</v>
+      <c r="L71" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="M71" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N71" s="11" t="s">
-        <v>22</v>
+      <c r="N71" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O71" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P71" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q71" s="17" t="s">
-        <v>22</v>
+      <c r="P71" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q71" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:17">
       <c r="A72" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="E72" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G72" s="11" t="s">
-        <v>22</v>
+      <c r="G72" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H72" s="11" t="s">
         <v>22</v>
@@ -6264,14 +6378,14 @@
       <c r="I72" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J72" s="12" t="s">
-        <v>23</v>
+      <c r="J72" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L72" s="11" t="s">
-        <v>22</v>
+      <c r="L72" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="M72" s="11" t="s">
         <v>22</v>
@@ -6285,25 +6399,25 @@
       <c r="P72" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q72" s="17" t="s">
-        <v>22</v>
+      <c r="Q72" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:17">
       <c r="A73" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="E73" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>22</v>
@@ -6335,28 +6449,28 @@
       <c r="O73" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q73" s="17" t="s">
-        <v>22</v>
+      <c r="P73" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q73" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:17">
       <c r="A74" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="E74" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>22</v>
@@ -6388,28 +6502,28 @@
       <c r="O74" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P74" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q74" s="17" t="s">
-        <v>22</v>
+      <c r="P74" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q74" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:17">
       <c r="A75" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="E75" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>22</v>
@@ -6450,19 +6564,19 @@
     </row>
     <row r="76" customHeight="1" spans="1:17">
       <c r="A76" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="E76" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>22</v>
@@ -6494,28 +6608,28 @@
       <c r="O76" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P76" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q76" s="17" t="s">
-        <v>22</v>
+      <c r="P76" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q76" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:17">
       <c r="A77" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E77" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>22</v>
@@ -6532,8 +6646,8 @@
       <c r="J77" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K77" s="11" t="s">
-        <v>22</v>
+      <c r="K77" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L77" s="11" t="s">
         <v>22</v>
@@ -6550,25 +6664,25 @@
       <c r="P77" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q77" s="11" t="s">
+      <c r="Q77" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:17">
       <c r="A78" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E78" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>22</v>
@@ -6585,8 +6699,8 @@
       <c r="J78" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K78" s="11" t="s">
-        <v>22</v>
+      <c r="K78" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L78" s="11" t="s">
         <v>22</v>
@@ -6603,25 +6717,25 @@
       <c r="P78" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q78" s="11" t="s">
+      <c r="Q78" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:17">
       <c r="A79" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E79" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F79" s="11" t="s">
         <v>22</v>
@@ -6635,11 +6749,11 @@
       <c r="I79" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J79" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K79" s="11" t="s">
-        <v>22</v>
+      <c r="J79" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K79" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L79" s="11" t="s">
         <v>22</v>
@@ -6653,8 +6767,8 @@
       <c r="O79" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P79" s="12" t="s">
-        <v>23</v>
+      <c r="P79" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q79" s="17" t="s">
         <v>22</v>
@@ -6662,19 +6776,19 @@
     </row>
     <row r="80" customHeight="1" spans="1:17">
       <c r="A80" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>22</v>
@@ -6688,11 +6802,11 @@
       <c r="I80" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J80" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K80" s="11" t="s">
-        <v>22</v>
+      <c r="J80" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K80" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L80" s="11" t="s">
         <v>22</v>
@@ -6700,8 +6814,8 @@
       <c r="M80" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N80" s="12" t="s">
-        <v>23</v>
+      <c r="N80" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O80" s="11" t="s">
         <v>22</v>
@@ -6715,68 +6829,662 @@
     </row>
     <row r="81" customHeight="1" spans="1:17">
       <c r="A81" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K81" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P81" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q81" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:17">
+      <c r="A82" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C82" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E82" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J82" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P82" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q82" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:17">
+      <c r="A83" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="E81" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N81" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P81" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q81" s="17" t="s">
+      <c r="B83" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E83" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P83" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q83" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:17">
+      <c r="A84" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E84" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J84" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P84" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q84" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:17">
+      <c r="A85" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E85" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J85" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P85" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q85" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:17">
+      <c r="A86" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E86" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J86" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P86" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q86" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:17">
+      <c r="A87" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E87" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P87" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q87" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:17">
+      <c r="A88" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E88" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J88" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P88" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q88" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:17">
+      <c r="A89" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E89" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J89" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q89" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:17">
+      <c r="A90" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E90" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O90" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P90" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q90" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:17">
+      <c r="A91" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E91" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N91" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P91" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q91" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:17">
+      <c r="A92" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E92" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N92" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P92" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q92" s="17" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D28" r:id="rId1" display="https://legacy-docs.dify.ai/zh-hans"/>
+    <hyperlink ref="D31" r:id="rId1" display="https://legacy-docs.dify.ai/zh-hans"/>
     <hyperlink ref="D3" r:id="rId2" display="https://platform.deepseek.com"/>
     <hyperlink ref="D4" r:id="rId3" display="https://skills.sh" tooltip="https://skills.sh"/>
+    <hyperlink ref="D35" r:id="rId4" display="https://uiverse.io" tooltip="https://uiverse.io"/>
+    <hyperlink ref="D36" r:id="rId5" display="https://inspira-ui.com/docs/cn" tooltip="https://inspira-ui.com/docs/cn"/>
+    <hyperlink ref="D60" r:id="rId6" display="https://color.review" tooltip="https://color.review"/>
+    <hyperlink ref="D37" r:id="rId7" display="https://www.patterns.dev" tooltip="https://www.patterns.dev"/>
+    <hyperlink ref="D65" r:id="rId8" display="https://color.adobe.com/zh"/>
+    <hyperlink ref="D43" r:id="rId9" display="https://std.samr.gov.cn"/>
+    <hyperlink ref="D44" r:id="rId10" display="https://openstd.samr.gov.cn/bzgk/gb/index"/>
+    <hyperlink ref="D42" r:id="rId11" display="https://www.stats.gov.cn"/>
+    <hyperlink ref="D30" r:id="rId12" display="https://tldr.sh"/>
+    <hyperlink ref="D58" r:id="rId13" display="https://chalk.ist"/>
+    <hyperlink ref="D26" r:id="rId14" display="https://nix.dev"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="33" orientation="portrait"/>
   <headerFooter/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="92" max="16" man="1"/>
+    <brk id="103" max="16" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="5" max="1048575" man="1"/>
@@ -6856,19 +7564,19 @@
     </row>
     <row r="2" customHeight="1" spans="1:17">
       <c r="A2" s="9" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>22</v>
@@ -6909,19 +7617,19 @@
     </row>
     <row r="3" customHeight="1" spans="1:17">
       <c r="A3" s="9" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>22</v>
@@ -6962,19 +7670,19 @@
     </row>
     <row r="4" customHeight="1" spans="1:17">
       <c r="A4" s="9" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="D4" s="9">
         <v>2</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>22</v>
@@ -7015,19 +7723,19 @@
     </row>
     <row r="5" customHeight="1" spans="1:17">
       <c r="A5" s="9" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="D5" s="9">
         <v>3</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>22</v>
@@ -7068,19 +7776,19 @@
     </row>
     <row r="6" customHeight="1" spans="1:17">
       <c r="A6" s="9" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="D6" s="9">
         <v>4</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>22</v>
@@ -7121,19 +7829,19 @@
     </row>
     <row r="7" customHeight="1" spans="1:17">
       <c r="A7" s="9" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="D7" s="9">
         <v>5</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>22</v>
@@ -7174,19 +7882,19 @@
     </row>
     <row r="8" customHeight="1" spans="1:17">
       <c r="A8" s="9" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="D8" s="9">
         <v>6</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>22</v>
@@ -7227,19 +7935,19 @@
     </row>
     <row r="9" customHeight="1" spans="1:17">
       <c r="A9" s="9" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="D9" s="9">
         <v>7</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>22</v>
@@ -7280,19 +7988,19 @@
     </row>
     <row r="10" customHeight="1" spans="1:17">
       <c r="A10" s="9" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="D10" s="9">
         <v>8</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>22</v>
@@ -7333,19 +8041,19 @@
     </row>
     <row r="11" customHeight="1" spans="1:17">
       <c r="A11" s="9" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="D11" s="9">
         <v>9</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>22</v>
@@ -7386,19 +8094,19 @@
     </row>
     <row r="12" customHeight="1" spans="1:17">
       <c r="A12" s="9" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="D12" s="9">
         <v>10</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>22</v>
@@ -7439,19 +8147,19 @@
     </row>
     <row r="13" customHeight="1" spans="1:17">
       <c r="A13" s="9" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>349</v>
+        <v>387</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="D13" s="9">
         <v>11</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>22</v>
@@ -7492,19 +8200,19 @@
     </row>
     <row r="14" customHeight="1" spans="1:17">
       <c r="A14" s="9" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>22</v>
@@ -7545,19 +8253,19 @@
     </row>
     <row r="15" customHeight="1" spans="1:17">
       <c r="A15" s="9" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>22</v>
@@ -7598,19 +8306,19 @@
     </row>
     <row r="16" customHeight="1" spans="1:17">
       <c r="A16" s="9" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
@@ -7651,19 +8359,19 @@
     </row>
     <row r="17" customHeight="1" spans="1:17">
       <c r="A17" s="9" t="s">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>22</v>
@@ -7704,19 +8412,19 @@
     </row>
     <row r="18" customHeight="1" spans="1:17">
       <c r="A18" s="9" t="s">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>22</v>
@@ -7757,19 +8465,19 @@
     </row>
     <row r="19" customHeight="1" spans="1:17">
       <c r="A19" s="9" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>374</v>
+        <v>412</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>22</v>
@@ -7810,19 +8518,19 @@
     </row>
     <row r="20" customHeight="1" spans="1:17">
       <c r="A20" s="9" t="s">
-        <v>375</v>
+        <v>413</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>22</v>
@@ -7863,19 +8571,19 @@
     </row>
     <row r="21" customHeight="1" spans="1:17">
       <c r="A21" s="2" t="s">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>380</v>
+        <v>418</v>
       </c>
       <c r="D21" s="2">
         <v>13</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>22</v>
@@ -7916,19 +8624,19 @@
     </row>
     <row r="22" customHeight="1" spans="1:17">
       <c r="A22" s="9" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>382</v>
+        <v>420</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>383</v>
+        <v>421</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>384</v>
+        <v>422</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>22</v>
@@ -7969,19 +8677,19 @@
     </row>
     <row r="23" customHeight="1" spans="1:17">
       <c r="A23" s="2" t="s">
-        <v>385</v>
+        <v>423</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>387</v>
+        <v>425</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>22</v>
@@ -8022,19 +8730,19 @@
     </row>
     <row r="24" customHeight="1" spans="1:17">
       <c r="A24" s="2" t="s">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
@@ -8075,19 +8783,19 @@
     </row>
     <row r="25" customHeight="1" spans="1:17">
       <c r="A25" s="2" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>394</v>
+        <v>432</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>395</v>
+        <v>433</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>23</v>
@@ -8128,19 +8836,19 @@
     </row>
     <row r="26" customHeight="1" spans="1:17">
       <c r="A26" s="9" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>399</v>
+        <v>437</v>
       </c>
       <c r="D26" s="9">
         <v>15</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>23</v>
@@ -8181,19 +8889,19 @@
     </row>
     <row r="27" customHeight="1" spans="1:17">
       <c r="A27" s="9" t="s">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>403</v>
+        <v>441</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>23</v>
@@ -8234,19 +8942,19 @@
     </row>
     <row r="28" customHeight="1" spans="1:17">
       <c r="A28" s="9" t="s">
-        <v>404</v>
+        <v>442</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>405</v>
+        <v>443</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>406</v>
+        <v>444</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>407</v>
+        <v>445</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>23</v>
@@ -8287,19 +8995,19 @@
     </row>
     <row r="29" customHeight="1" spans="1:17">
       <c r="A29" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="E29" s="14" t="s">
         <v>408</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>370</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>23</v>
@@ -8340,19 +9048,19 @@
     </row>
     <row r="30" customHeight="1" spans="1:17">
       <c r="A30" s="9" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>414</v>
+        <v>452</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>23</v>
@@ -8393,19 +9101,19 @@
     </row>
     <row r="31" customHeight="1" spans="1:17">
       <c r="A31" s="9" t="s">
-        <v>416</v>
+        <v>454</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>417</v>
+        <v>455</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>418</v>
+        <v>456</v>
       </c>
       <c r="D31" s="9">
         <v>12</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>23</v>

--- a/instance/data-human.xlsx
+++ b/instance/data-human.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28470" windowHeight="12043"/>
+    <workbookView windowWidth="28470" windowHeight="12043" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Navigation" sheetId="1" r:id="rId1"/>
     <sheet name="Service" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Navigation!$A$1:$Q$111</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Navigation!$A$1:$Q$114</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="469">
   <si>
     <t>名称</t>
   </si>
@@ -441,6 +441,30 @@
     <t>https://legacy-docs.dify.ai/zh-hans</t>
   </si>
   <si>
+    <t>Vue</t>
+  </si>
+  <si>
+    <t>Vue 官方手册</t>
+  </si>
+  <si>
+    <t>vue.png</t>
+  </si>
+  <si>
+    <t>https://cn.vuejs.org/guide/introduction.html</t>
+  </si>
+  <si>
+    <t>Tauri</t>
+  </si>
+  <si>
+    <t>Tauri 官方手册</t>
+  </si>
+  <si>
+    <t>tauri.png</t>
+  </si>
+  <si>
+    <t>https://www.tauri.net.cn/guides</t>
+  </si>
+  <si>
     <t>Tailwindcss</t>
   </si>
   <si>
@@ -861,6 +885,18 @@
     <t>https://halftone.xoihazard.com</t>
   </si>
   <si>
+    <t>Color Flow</t>
+  </si>
+  <si>
+    <t>渐变背景生成工具</t>
+  </si>
+  <si>
+    <t>colorflow.png</t>
+  </si>
+  <si>
+    <t>https://colorflow.ls.graphics</t>
+  </si>
+  <si>
     <t>Shots</t>
   </si>
   <si>
@@ -1278,7 +1314,7 @@
     <t>Agentic AI 管理后台</t>
   </si>
   <si>
-    <t>http://192.168.31.96:10080/apps</t>
+    <t>http://192.168.31.97:10080/apps</t>
   </si>
   <si>
     <t>* Icraft Editor</t>
@@ -1335,7 +1371,7 @@
     <t>vaultwarden.png</t>
   </si>
   <si>
-    <t>http://192.168.31.96:8222</t>
+    <t>http://192.168.31.97:8222</t>
   </si>
   <si>
     <t>* Invoice Assistant</t>
@@ -2575,7 +2611,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:R95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.625" style="2" customWidth="1"/>
@@ -4284,13 +4320,13 @@
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:17">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="9" t="s">
         <v>142</v>
       </c>
       <c r="D33" s="9" t="s">
@@ -4337,17 +4373,17 @@
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:17">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="B34" s="9" t="s">
         <v>145</v>
       </c>
+      <c r="C34" s="9" t="s">
+        <v>146</v>
+      </c>
       <c r="D34" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>103</v>
@@ -4391,16 +4427,16 @@
     </row>
     <row r="35" customHeight="1" spans="1:17">
       <c r="A35" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>103</v>
@@ -4444,16 +4480,16 @@
     </row>
     <row r="36" customHeight="1" spans="1:17">
       <c r="A36" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>103</v>
@@ -4497,10 +4533,10 @@
     </row>
     <row r="37" customHeight="1" spans="1:17">
       <c r="A37" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>156</v>
@@ -4579,8 +4615,8 @@
       <c r="J38" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="11" t="s">
-        <v>22</v>
+      <c r="K38" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L38" s="11" t="s">
         <v>22</v>
@@ -4591,11 +4627,11 @@
       <c r="N38" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P38" s="12" t="s">
-        <v>23</v>
+      <c r="O38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P38" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q38" s="17" t="s">
         <v>22</v>
@@ -4617,29 +4653,29 @@
       <c r="E39" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F39" s="12" t="s">
-        <v>23</v>
+      <c r="F39" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="G39" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>22</v>
+      <c r="H39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L39" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M39" s="12" t="s">
-        <v>23</v>
+      <c r="M39" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="N39" s="11" t="s">
         <v>22</v>
@@ -4647,8 +4683,8 @@
       <c r="O39" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P39" s="12" t="s">
-        <v>23</v>
+      <c r="P39" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q39" s="17" t="s">
         <v>22</v>
@@ -4670,17 +4706,17 @@
       <c r="E40" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F40" s="12" t="s">
-        <v>23</v>
+      <c r="F40" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="G40" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="12" t="s">
-        <v>23</v>
+      <c r="H40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>22</v>
@@ -4691,17 +4727,17 @@
       <c r="L40" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M40" s="12" t="s">
-        <v>23</v>
+      <c r="M40" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="N40" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O40" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P40" s="11" t="s">
-        <v>22</v>
+      <c r="O40" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P40" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="Q40" s="17" t="s">
         <v>22</v>
@@ -4715,10 +4751,10 @@
         <v>171</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>103</v>
@@ -4735,8 +4771,8 @@
       <c r="I41" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J41" s="11" t="s">
-        <v>22</v>
+      <c r="J41" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>22</v>
@@ -4753,8 +4789,8 @@
       <c r="O41" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P41" s="11" t="s">
-        <v>22</v>
+      <c r="P41" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="Q41" s="17" t="s">
         <v>22</v>
@@ -4762,16 +4798,16 @@
     </row>
     <row r="42" customHeight="1" spans="1:17">
       <c r="A42" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>103</v>
@@ -4815,16 +4851,16 @@
     </row>
     <row r="43" customHeight="1" spans="1:17">
       <c r="A43" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D43" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>103</v>
@@ -4868,16 +4904,16 @@
     </row>
     <row r="44" customHeight="1" spans="1:17">
       <c r="A44" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>103</v>
@@ -4921,31 +4957,31 @@
     </row>
     <row r="45" customHeight="1" spans="1:17">
       <c r="A45" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F45" s="11" t="s">
-        <v>22</v>
+      <c r="F45" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>22</v>
+      <c r="H45" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>22</v>
@@ -4956,11 +4992,11 @@
       <c r="L45" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M45" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N45" s="12" t="s">
-        <v>23</v>
+      <c r="M45" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N45" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O45" s="11" t="s">
         <v>22</v>
@@ -4972,33 +5008,33 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" s="16" customFormat="1" customHeight="1" spans="1:17">
+    <row r="46" customHeight="1" spans="1:17">
       <c r="A46" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>188</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F46" s="11" t="s">
-        <v>22</v>
+      <c r="F46" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="11" t="s">
-        <v>22</v>
+      <c r="H46" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>22</v>
@@ -5009,197 +5045,197 @@
       <c r="L46" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M46" s="11" t="s">
-        <v>22</v>
+      <c r="M46" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="N46" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O46" s="12" t="s">
-        <v>23</v>
+      <c r="O46" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="P46" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q46" s="12" t="s">
-        <v>23</v>
+      <c r="Q46" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:17">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="E47" s="23" t="s">
+      <c r="E47" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q47" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" s="16" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A48" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="K47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="M47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="O47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P47" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q47" s="21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="1:17">
-      <c r="A48" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E48" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N48" s="12" t="s">
-        <v>23</v>
+      <c r="E48" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N48" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O48" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P48" s="12" t="s">
-        <v>23</v>
+      <c r="P48" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q48" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:17">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P49" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q49" s="12" t="s">
+      <c r="E49" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P49" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q49" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:17">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E50" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E50" s="24" t="s">
-        <v>193</v>
-      </c>
       <c r="F50" s="12" t="s">
         <v>23</v>
       </c>
@@ -5238,20 +5274,20 @@
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:17">
-      <c r="A51" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B51" s="9" t="s">
+      <c r="A51" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="B51" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="C51" s="2" t="s">
         <v>207</v>
       </c>
+      <c r="D51" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="E51" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>23</v>
@@ -5292,108 +5328,108 @@
     </row>
     <row r="52" customHeight="1" spans="1:17">
       <c r="A52" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>210</v>
+        <v>26</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>211</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N52" s="11" t="s">
-        <v>22</v>
+        <v>201</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O52" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q52" s="17" t="s">
-        <v>22</v>
+      <c r="P52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q52" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:17">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="9" t="s">
         <v>215</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N53" s="11" t="s">
-        <v>22</v>
+        <v>201</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O53" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q53" s="17" t="s">
-        <v>22</v>
+      <c r="P53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q53" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:17">
@@ -5410,7 +5446,7 @@
         <v>219</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>22</v>
@@ -5450,20 +5486,20 @@
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:17">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="2" t="s">
         <v>223</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>22</v>
@@ -5516,7 +5552,7 @@
         <v>227</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>22</v>
@@ -5569,7 +5605,7 @@
         <v>231</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>22</v>
@@ -5586,8 +5622,8 @@
       <c r="J57" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K57" s="12" t="s">
-        <v>23</v>
+      <c r="K57" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L57" s="11" t="s">
         <v>22</v>
@@ -5622,7 +5658,7 @@
         <v>235</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>22</v>
@@ -5639,8 +5675,8 @@
       <c r="J58" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K58" s="12" t="s">
-        <v>23</v>
+      <c r="K58" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L58" s="11" t="s">
         <v>22</v>
@@ -5662,20 +5698,20 @@
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:17">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="9" t="s">
         <v>239</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>22</v>
@@ -5704,8 +5740,8 @@
       <c r="N59" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O59" s="11" t="s">
-        <v>22</v>
+      <c r="O59" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P59" s="11" t="s">
         <v>22</v>
@@ -5715,20 +5751,20 @@
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:17">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="9" t="s">
         <v>243</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>22</v>
@@ -5757,8 +5793,8 @@
       <c r="N60" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O60" s="11" t="s">
-        <v>22</v>
+      <c r="O60" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P60" s="11" t="s">
         <v>22</v>
@@ -5768,26 +5804,26 @@
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:17">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="2" t="s">
         <v>247</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="12" t="s">
-        <v>23</v>
+      <c r="G61" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>22</v>
@@ -5795,11 +5831,11 @@
       <c r="I61" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J61" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K61" s="11" t="s">
-        <v>22</v>
+      <c r="J61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K61" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L61" s="11" t="s">
         <v>22</v>
@@ -5813,34 +5849,34 @@
       <c r="O61" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P61" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q61" s="12" t="s">
-        <v>23</v>
+      <c r="P61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q61" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:17">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="2" t="s">
         <v>251</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G62" s="12" t="s">
-        <v>23</v>
+      <c r="G62" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H62" s="11" t="s">
         <v>22</v>
@@ -5848,11 +5884,11 @@
       <c r="I62" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J62" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K62" s="11" t="s">
-        <v>22</v>
+      <c r="J62" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K62" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L62" s="11" t="s">
         <v>22</v>
@@ -5866,34 +5902,34 @@
       <c r="O62" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P62" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q62" s="12" t="s">
-        <v>23</v>
+      <c r="P62" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q62" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:17">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="9" t="s">
         <v>255</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G63" s="11" t="s">
-        <v>22</v>
+      <c r="G63" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H63" s="11" t="s">
         <v>22</v>
@@ -5919,34 +5955,34 @@
       <c r="O63" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P63" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q63" s="17" t="s">
-        <v>22</v>
+      <c r="P63" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q63" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:17">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="9" t="s">
         <v>259</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G64" s="11" t="s">
-        <v>22</v>
+      <c r="G64" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H64" s="11" t="s">
         <v>22</v>
@@ -5972,14 +6008,14 @@
       <c r="O64" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P64" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q64" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:17">
+      <c r="P64" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q64" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:18">
       <c r="A65" s="2" t="s">
         <v>260</v>
       </c>
@@ -5993,7 +6029,7 @@
         <v>263</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>22</v>
@@ -6032,7 +6068,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:17">
+    <row r="66" customHeight="1" spans="1:18">
       <c r="A66" s="2" t="s">
         <v>264</v>
       </c>
@@ -6046,7 +6082,7 @@
         <v>267</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>22</v>
@@ -6085,11 +6121,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:17">
+    <row r="67" customHeight="1" spans="1:18">
       <c r="A67" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B67" s="25" t="s">
+      <c r="B67" s="2" t="s">
         <v>269</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -6099,7 +6135,7 @@
         <v>271</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>22</v>
@@ -6138,7 +6174,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:17">
+    <row r="68" customHeight="1" spans="1:18">
       <c r="A68" s="2" t="s">
         <v>272</v>
       </c>
@@ -6152,7 +6188,7 @@
         <v>275</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>22</v>
@@ -6191,11 +6227,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" s="16" customFormat="1" customHeight="1" spans="1:17">
+    <row r="69" customHeight="1" spans="1:18">
       <c r="A69" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="25" t="s">
         <v>277</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -6205,7 +6241,7 @@
         <v>279</v>
       </c>
       <c r="E69" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>22</v>
@@ -6244,60 +6280,60 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:17">
-      <c r="A70" s="15" t="s">
+    <row r="70" customHeight="1" spans="1:18">
+      <c r="A70" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C70" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="D70" s="15" t="s">
+      <c r="C70" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="E70" s="26" t="s">
+      <c r="D70" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F70" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G70" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H70" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I70" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J70" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="K70" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="L70" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="M70" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N70" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="O70" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="P70" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q70" s="22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="1:17">
+      <c r="E70" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J70" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P70" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q70" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" customHeight="1" spans="1:18">
       <c r="A71" s="2" t="s">
         <v>284</v>
       </c>
@@ -6310,14 +6346,14 @@
       <c r="D71" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="E71" s="27" t="s">
-        <v>283</v>
+      <c r="E71" s="24" t="s">
+        <v>201</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G71" s="12" t="s">
-        <v>23</v>
+      <c r="G71" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H71" s="11" t="s">
         <v>22</v>
@@ -6331,26 +6367,27 @@
       <c r="K71" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L71" s="12" t="s">
-        <v>23</v>
+      <c r="L71" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="M71" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N71" s="12" t="s">
-        <v>23</v>
+      <c r="N71" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O71" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P71" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q71" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:17">
+      <c r="P71" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q71" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="R71" s="2"/>
+    </row>
+    <row r="72" s="16" customFormat="1" customHeight="1" spans="1:18">
       <c r="A72" s="2" t="s">
         <v>288</v>
       </c>
@@ -6363,14 +6400,14 @@
       <c r="D72" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E72" s="27" t="s">
-        <v>283</v>
+      <c r="E72" s="24" t="s">
+        <v>201</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G72" s="12" t="s">
-        <v>23</v>
+      <c r="G72" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H72" s="11" t="s">
         <v>22</v>
@@ -6378,14 +6415,14 @@
       <c r="I72" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J72" s="11" t="s">
-        <v>22</v>
+      <c r="J72" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L72" s="12" t="s">
-        <v>23</v>
+      <c r="L72" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="M72" s="11" t="s">
         <v>22</v>
@@ -6399,64 +6436,64 @@
       <c r="P72" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q72" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:17">
-      <c r="A73" s="2" t="s">
+      <c r="Q72" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:18">
+      <c r="A73" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D73" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="E73" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="F73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J73" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O73" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P73" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q73" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="1:17">
+      <c r="F73" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K73" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L73" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M73" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N73" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O73" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="P73" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q73" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:18">
       <c r="A74" s="2" t="s">
         <v>296</v>
       </c>
@@ -6470,13 +6507,13 @@
         <v>299</v>
       </c>
       <c r="E74" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G74" s="11" t="s">
-        <v>22</v>
+      <c r="G74" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H74" s="11" t="s">
         <v>22</v>
@@ -6490,14 +6527,14 @@
       <c r="K74" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L74" s="11" t="s">
-        <v>22</v>
+      <c r="L74" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="M74" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N74" s="11" t="s">
-        <v>22</v>
+      <c r="N74" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O74" s="11" t="s">
         <v>22</v>
@@ -6509,27 +6546,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:17">
+    <row r="75" customHeight="1" spans="1:18">
       <c r="A75" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E75" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G75" s="11" t="s">
-        <v>22</v>
+      <c r="G75" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H75" s="11" t="s">
         <v>22</v>
@@ -6537,14 +6574,14 @@
       <c r="I75" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J75" s="12" t="s">
-        <v>23</v>
+      <c r="J75" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="K75" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L75" s="11" t="s">
-        <v>22</v>
+      <c r="L75" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="M75" s="11" t="s">
         <v>22</v>
@@ -6555,28 +6592,28 @@
       <c r="O75" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P75" s="12" t="s">
-        <v>23</v>
+      <c r="P75" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q75" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:17">
+    <row r="76" customHeight="1" spans="1:18">
       <c r="A76" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E76" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>22</v>
@@ -6615,21 +6652,21 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:17">
+    <row r="77" customHeight="1" spans="1:18">
       <c r="A77" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E77" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>22</v>
@@ -6646,8 +6683,8 @@
       <c r="J77" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K77" s="12" t="s">
-        <v>23</v>
+      <c r="K77" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L77" s="11" t="s">
         <v>22</v>
@@ -6661,81 +6698,81 @@
       <c r="O77" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P77" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q77" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="1:17">
+      <c r="P77" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q77" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:18">
       <c r="A78" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="C78" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D78" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E78" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O78" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P78" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q78" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:18">
+      <c r="A79" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E78" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="F78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J78" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K78" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P78" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q78" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="1:17">
-      <c r="A79" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="E79" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F79" s="11" t="s">
         <v>22</v>
@@ -6752,8 +6789,8 @@
       <c r="J79" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K79" s="12" t="s">
-        <v>23</v>
+      <c r="K79" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L79" s="11" t="s">
         <v>22</v>
@@ -6767,28 +6804,28 @@
       <c r="O79" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P79" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q79" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="1:17">
+      <c r="P79" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q79" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:18">
       <c r="A80" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>22</v>
@@ -6829,10 +6866,10 @@
     </row>
     <row r="81" customHeight="1" spans="1:17">
       <c r="A81" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>322</v>
@@ -6841,7 +6878,7 @@
         <v>323</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F81" s="11" t="s">
         <v>22</v>
@@ -6894,7 +6931,7 @@
         <v>327</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F82" s="11" t="s">
         <v>22</v>
@@ -6911,8 +6948,8 @@
       <c r="J82" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K82" s="11" t="s">
-        <v>22</v>
+      <c r="K82" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L82" s="11" t="s">
         <v>22</v>
@@ -6947,7 +6984,7 @@
         <v>331</v>
       </c>
       <c r="E83" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F83" s="11" t="s">
         <v>22</v>
@@ -6964,8 +7001,8 @@
       <c r="J83" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K83" s="11" t="s">
-        <v>22</v>
+      <c r="K83" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L83" s="11" t="s">
         <v>22</v>
@@ -7000,7 +7037,7 @@
         <v>335</v>
       </c>
       <c r="E84" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>22</v>
@@ -7017,8 +7054,8 @@
       <c r="J84" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K84" s="11" t="s">
-        <v>22</v>
+      <c r="K84" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L84" s="11" t="s">
         <v>22</v>
@@ -7047,13 +7084,13 @@
         <v>337</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>50</v>
+        <v>338</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E85" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>22</v>
@@ -7094,19 +7131,19 @@
     </row>
     <row r="86" customHeight="1" spans="1:17">
       <c r="A86" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E86" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>22</v>
@@ -7138,28 +7175,28 @@
       <c r="O86" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P86" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q86" s="12" t="s">
-        <v>23</v>
+      <c r="P86" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q86" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:17">
       <c r="A87" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E87" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F87" s="11" t="s">
         <v>22</v>
@@ -7200,19 +7237,19 @@
     </row>
     <row r="88" customHeight="1" spans="1:17">
       <c r="A88" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>349</v>
+        <v>50</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>350</v>
       </c>
       <c r="E88" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>22</v>
@@ -7247,7 +7284,7 @@
       <c r="P88" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q88" s="11" t="s">
+      <c r="Q88" s="17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -7265,7 +7302,7 @@
         <v>354</v>
       </c>
       <c r="E89" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F89" s="11" t="s">
         <v>22</v>
@@ -7297,11 +7334,11 @@
       <c r="O89" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P89" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q89" s="11" t="s">
-        <v>22</v>
+      <c r="P89" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q89" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:17">
@@ -7318,7 +7355,7 @@
         <v>358</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>22</v>
@@ -7332,8 +7369,8 @@
       <c r="I90" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J90" s="11" t="s">
-        <v>22</v>
+      <c r="J90" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K90" s="11" t="s">
         <v>22</v>
@@ -7350,8 +7387,8 @@
       <c r="O90" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P90" s="12" t="s">
-        <v>23</v>
+      <c r="P90" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q90" s="17" t="s">
         <v>22</v>
@@ -7371,7 +7408,7 @@
         <v>362</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F91" s="11" t="s">
         <v>22</v>
@@ -7385,8 +7422,8 @@
       <c r="I91" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J91" s="11" t="s">
-        <v>22</v>
+      <c r="J91" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K91" s="11" t="s">
         <v>22</v>
@@ -7397,8 +7434,8 @@
       <c r="M91" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N91" s="12" t="s">
-        <v>23</v>
+      <c r="N91" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O91" s="11" t="s">
         <v>22</v>
@@ -7406,7 +7443,7 @@
       <c r="P91" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q91" s="17" t="s">
+      <c r="Q91" s="11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -7424,7 +7461,7 @@
         <v>366</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>22</v>
@@ -7438,8 +7475,8 @@
       <c r="I92" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J92" s="11" t="s">
-        <v>22</v>
+      <c r="J92" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K92" s="11" t="s">
         <v>22</v>
@@ -7450,8 +7487,8 @@
       <c r="M92" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N92" s="12" t="s">
-        <v>23</v>
+      <c r="N92" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O92" s="11" t="s">
         <v>22</v>
@@ -7459,7 +7496,166 @@
       <c r="P92" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q92" s="17" t="s">
+      <c r="Q92" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:17">
+      <c r="A93" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E93" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P93" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q93" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:17">
+      <c r="A94" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E94" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N94" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P94" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q94" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:17">
+      <c r="A95" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E95" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N95" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P95" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q95" s="17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -7468,23 +7664,26 @@
     <hyperlink ref="D31" r:id="rId1" display="https://legacy-docs.dify.ai/zh-hans"/>
     <hyperlink ref="D3" r:id="rId2" display="https://platform.deepseek.com"/>
     <hyperlink ref="D4" r:id="rId3" display="https://skills.sh" tooltip="https://skills.sh"/>
-    <hyperlink ref="D35" r:id="rId4" display="https://uiverse.io" tooltip="https://uiverse.io"/>
-    <hyperlink ref="D36" r:id="rId5" display="https://inspira-ui.com/docs/cn" tooltip="https://inspira-ui.com/docs/cn"/>
-    <hyperlink ref="D60" r:id="rId6" display="https://color.review" tooltip="https://color.review"/>
-    <hyperlink ref="D37" r:id="rId7" display="https://www.patterns.dev" tooltip="https://www.patterns.dev"/>
-    <hyperlink ref="D65" r:id="rId8" display="https://color.adobe.com/zh"/>
-    <hyperlink ref="D43" r:id="rId9" display="https://std.samr.gov.cn"/>
-    <hyperlink ref="D44" r:id="rId10" display="https://openstd.samr.gov.cn/bzgk/gb/index"/>
-    <hyperlink ref="D42" r:id="rId11" display="https://www.stats.gov.cn"/>
+    <hyperlink ref="D37" r:id="rId4" display="https://uiverse.io" tooltip="https://uiverse.io"/>
+    <hyperlink ref="D38" r:id="rId5" display="https://inspira-ui.com/docs/cn" tooltip="https://inspira-ui.com/docs/cn"/>
+    <hyperlink ref="D62" r:id="rId6" display="https://color.review" tooltip="https://color.review"/>
+    <hyperlink ref="D39" r:id="rId7" display="https://www.patterns.dev" tooltip="https://www.patterns.dev"/>
+    <hyperlink ref="D67" r:id="rId8" display="https://color.adobe.com/zh"/>
+    <hyperlink ref="D45" r:id="rId9" display="https://std.samr.gov.cn"/>
+    <hyperlink ref="D46" r:id="rId10" display="https://openstd.samr.gov.cn/bzgk/gb/index"/>
+    <hyperlink ref="D44" r:id="rId11" display="https://www.stats.gov.cn"/>
     <hyperlink ref="D30" r:id="rId12" display="https://tldr.sh"/>
-    <hyperlink ref="D58" r:id="rId13" display="https://chalk.ist"/>
+    <hyperlink ref="D60" r:id="rId13" display="https://chalk.ist"/>
     <hyperlink ref="D26" r:id="rId14" display="https://nix.dev"/>
+    <hyperlink ref="D32" r:id="rId15" display="https://cn.vuejs.org/guide/introduction.html"/>
+    <hyperlink ref="D33" r:id="rId16" display="https://www.tauri.net.cn/guides"/>
+    <hyperlink ref="D71" r:id="rId17" display="https://colorflow.ls.graphics" tooltip="https://colorflow.ls.graphics"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="33" orientation="portrait"/>
   <headerFooter/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="103" max="16" man="1"/>
+    <brk id="106" max="16" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="5" max="1048575" man="1"/>
@@ -7564,19 +7763,19 @@
     </row>
     <row r="2" customHeight="1" spans="1:17">
       <c r="A2" s="9" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>22</v>
@@ -7617,19 +7816,19 @@
     </row>
     <row r="3" customHeight="1" spans="1:17">
       <c r="A3" s="9" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>22</v>
@@ -7670,19 +7869,19 @@
     </row>
     <row r="4" customHeight="1" spans="1:17">
       <c r="A4" s="9" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D4" s="9">
         <v>2</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>22</v>
@@ -7723,19 +7922,19 @@
     </row>
     <row r="5" customHeight="1" spans="1:17">
       <c r="A5" s="9" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D5" s="9">
         <v>3</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>22</v>
@@ -7776,19 +7975,19 @@
     </row>
     <row r="6" customHeight="1" spans="1:17">
       <c r="A6" s="9" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D6" s="9">
         <v>4</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>22</v>
@@ -7829,19 +8028,19 @@
     </row>
     <row r="7" customHeight="1" spans="1:17">
       <c r="A7" s="9" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D7" s="9">
         <v>5</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>22</v>
@@ -7882,19 +8081,19 @@
     </row>
     <row r="8" customHeight="1" spans="1:17">
       <c r="A8" s="9" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D8" s="9">
         <v>6</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>22</v>
@@ -7935,19 +8134,19 @@
     </row>
     <row r="9" customHeight="1" spans="1:17">
       <c r="A9" s="9" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D9" s="9">
         <v>7</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>22</v>
@@ -7988,19 +8187,19 @@
     </row>
     <row r="10" customHeight="1" spans="1:17">
       <c r="A10" s="9" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="D10" s="9">
         <v>8</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>22</v>
@@ -8041,19 +8240,19 @@
     </row>
     <row r="11" customHeight="1" spans="1:17">
       <c r="A11" s="9" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="D11" s="9">
         <v>9</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>22</v>
@@ -8094,19 +8293,19 @@
     </row>
     <row r="12" customHeight="1" spans="1:17">
       <c r="A12" s="9" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="D12" s="9">
         <v>10</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>22</v>
@@ -8147,19 +8346,19 @@
     </row>
     <row r="13" customHeight="1" spans="1:17">
       <c r="A13" s="9" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="D13" s="9">
         <v>11</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>22</v>
@@ -8200,19 +8399,19 @@
     </row>
     <row r="14" customHeight="1" spans="1:17">
       <c r="A14" s="9" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>22</v>
@@ -8253,19 +8452,19 @@
     </row>
     <row r="15" customHeight="1" spans="1:17">
       <c r="A15" s="9" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>22</v>
@@ -8306,19 +8505,19 @@
     </row>
     <row r="16" customHeight="1" spans="1:17">
       <c r="A16" s="9" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
@@ -8359,19 +8558,19 @@
     </row>
     <row r="17" customHeight="1" spans="1:17">
       <c r="A17" s="9" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>405</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>393</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>22</v>
@@ -8412,19 +8611,19 @@
     </row>
     <row r="18" customHeight="1" spans="1:17">
       <c r="A18" s="9" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>22</v>
@@ -8465,19 +8664,19 @@
     </row>
     <row r="19" customHeight="1" spans="1:17">
       <c r="A19" s="9" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>22</v>
@@ -8518,19 +8717,19 @@
     </row>
     <row r="20" customHeight="1" spans="1:17">
       <c r="A20" s="9" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>134</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>22</v>
@@ -8571,19 +8770,19 @@
     </row>
     <row r="21" customHeight="1" spans="1:17">
       <c r="A21" s="2" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D21" s="2">
+        <v>430</v>
+      </c>
+      <c r="D21" s="9">
         <v>13</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>22</v>
@@ -8624,19 +8823,19 @@
     </row>
     <row r="22" customHeight="1" spans="1:17">
       <c r="A22" s="9" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>420</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>408</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>22</v>
@@ -8677,19 +8876,19 @@
     </row>
     <row r="23" customHeight="1" spans="1:17">
       <c r="A23" s="2" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>426</v>
+        <v>437</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>438</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>22</v>
@@ -8730,19 +8929,19 @@
     </row>
     <row r="24" customHeight="1" spans="1:17">
       <c r="A24" s="2" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>430</v>
+        <v>441</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>442</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
@@ -8783,19 +8982,19 @@
     </row>
     <row r="25" customHeight="1" spans="1:17">
       <c r="A25" s="2" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>434</v>
+        <v>445</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>23</v>
@@ -8836,19 +9035,19 @@
     </row>
     <row r="26" customHeight="1" spans="1:17">
       <c r="A26" s="9" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D26" s="9">
         <v>15</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>23</v>
@@ -8889,19 +9088,19 @@
     </row>
     <row r="27" customHeight="1" spans="1:17">
       <c r="A27" s="9" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>23</v>
@@ -8942,19 +9141,19 @@
     </row>
     <row r="28" customHeight="1" spans="1:17">
       <c r="A28" s="9" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>23</v>
@@ -8995,19 +9194,19 @@
     </row>
     <row r="29" customHeight="1" spans="1:17">
       <c r="A29" s="9" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>23</v>
@@ -9048,19 +9247,19 @@
     </row>
     <row r="30" customHeight="1" spans="1:17">
       <c r="A30" s="9" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>23</v>
@@ -9101,19 +9300,19 @@
     </row>
     <row r="31" customHeight="1" spans="1:17">
       <c r="A31" s="9" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="D31" s="9">
         <v>12</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>23</v>
@@ -9153,6 +9352,13 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D15" r:id="rId1" display="http://192.168.31.96:3000" tooltip="http://192.168.31.96:3000"/>
+    <hyperlink ref="D16" r:id="rId2" display="http://192.168.31.96:2017"/>
+    <hyperlink ref="D18" r:id="rId3" display="http://192.168.31.97:8384"/>
+    <hyperlink ref="D20" r:id="rId4" display="http://192.168.31.97:10080/apps"/>
+    <hyperlink ref="D25" r:id="rId5" display="http://192.168.31.97:8222"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/instance/data-human.xlsx
+++ b/instance/data-human.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Service" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Navigation!$A$1:$Q$114</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Navigation!$A$1:$Q$116</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="481">
   <si>
     <t>名称</t>
   </si>
@@ -117,6 +117,18 @@
     <t>https://platform.deepseek.com</t>
   </si>
   <si>
+    <t>123 云盘</t>
+  </si>
+  <si>
+    <t>云存储平台</t>
+  </si>
+  <si>
+    <t>123pan.png</t>
+  </si>
+  <si>
+    <t>https://www.123pan.com</t>
+  </si>
+  <si>
     <t>Skills</t>
   </si>
   <si>
@@ -1041,6 +1053,18 @@
     <t>https://svglogo.top/explore</t>
   </si>
   <si>
+    <t>Developer Icons</t>
+  </si>
+  <si>
+    <t>开发工具 SVG 图库</t>
+  </si>
+  <si>
+    <t>developer-icons.png</t>
+  </si>
+  <si>
+    <t>https://xandemon.github.io/developer-icons/icons/All</t>
+  </si>
+  <si>
     <t>NationalFlag</t>
   </si>
   <si>
@@ -1360,6 +1384,18 @@
   </si>
   <si>
     <t>https://github.com/drawdb-io/drawdb</t>
+  </si>
+  <si>
+    <t>Nocobase</t>
+  </si>
+  <si>
+    <t>项目管理器</t>
+  </si>
+  <si>
+    <t>nocobase.png</t>
+  </si>
+  <si>
+    <t>http://192.168.31.97:10180</t>
   </si>
   <si>
     <t>* Vaultwarden</t>
@@ -2611,7 +2647,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R95"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.625" style="2" customWidth="1"/>
@@ -2919,8 +2955,8 @@
       <c r="J6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="12" t="s">
-        <v>23</v>
+      <c r="K6" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>22</v>
@@ -2995,13 +3031,13 @@
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:17">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="9" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="9" t="s">
@@ -3154,13 +3190,13 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:17">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D11" s="9" t="s">
@@ -3260,16 +3296,16 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:17">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E13" s="13" t="s">
@@ -3331,8 +3367,8 @@
       <c r="F14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="12" t="s">
-        <v>23</v>
+      <c r="G14" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>22</v>
@@ -3340,29 +3376,29 @@
       <c r="I14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>23</v>
+      <c r="J14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q14" s="12" t="s">
-        <v>23</v>
+      <c r="N14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:17">
@@ -3384,8 +3420,8 @@
       <c r="F15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>22</v>
+      <c r="G15" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>22</v>
@@ -3399,23 +3435,23 @@
       <c r="K15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L15" s="11" t="s">
-        <v>22</v>
+      <c r="L15" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="11" t="s">
-        <v>22</v>
+      <c r="N15" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q15" s="17" t="s">
-        <v>22</v>
+      <c r="P15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:17">
@@ -3423,13 +3459,13 @@
         <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>21</v>
@@ -3473,10 +3509,10 @@
     </row>
     <row r="17" customHeight="1" spans="1:17">
       <c r="A17" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>81</v>
@@ -3499,8 +3535,8 @@
       <c r="I17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="11" t="s">
-        <v>22</v>
+      <c r="J17" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>22</v>
@@ -3520,8 +3556,8 @@
       <c r="P17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q17" s="12" t="s">
-        <v>23</v>
+      <c r="Q17" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:17">
@@ -3540,38 +3576,38 @@
       <c r="E18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>23</v>
+      <c r="F18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q18" s="12" t="s">
         <v>23</v>
@@ -3737,126 +3773,126 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:17">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:17">
+      <c r="A23" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="M22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="O22" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q22" s="22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" s="15" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A23" s="9" t="s">
+      <c r="B23" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="C23" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="D23" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O23" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q23" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" s="15" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A24" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q23" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:17">
-      <c r="A24" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
@@ -3909,7 +3945,7 @@
         <v>114</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>22</v>
@@ -3956,13 +3992,13 @@
         <v>116</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>22</v>
@@ -4003,19 +4039,19 @@
     </row>
     <row r="27" customHeight="1" spans="1:17">
       <c r="A27" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>19</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>22</v>
@@ -4056,19 +4092,19 @@
     </row>
     <row r="28" customHeight="1" spans="1:17">
       <c r="A28" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>22</v>
@@ -4108,20 +4144,20 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:17">
-      <c r="A29" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="A29" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="B29" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="C29" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>127</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>22</v>
@@ -4161,20 +4197,20 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:17">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="2" t="s">
         <v>130</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>131</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>22</v>
@@ -4223,11 +4259,11 @@
       <c r="C31" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="2" t="s">
         <v>135</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>22</v>
@@ -4280,7 +4316,7 @@
         <v>139</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>22</v>
@@ -4297,8 +4333,8 @@
       <c r="J32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K32" s="12" t="s">
-        <v>23</v>
+      <c r="K32" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L32" s="11" t="s">
         <v>22</v>
@@ -4309,8 +4345,8 @@
       <c r="N32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O32" s="11" t="s">
-        <v>22</v>
+      <c r="O32" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P32" s="11" t="s">
         <v>22</v>
@@ -4333,7 +4369,7 @@
         <v>143</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>22</v>
@@ -4386,7 +4422,7 @@
         <v>147</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>22</v>
@@ -4426,20 +4462,20 @@
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:17">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="9" t="s">
         <v>150</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>151</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>22</v>
@@ -4483,16 +4519,16 @@
         <v>152</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>22</v>
@@ -4533,19 +4569,19 @@
     </row>
     <row r="37" customHeight="1" spans="1:17">
       <c r="A37" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>22</v>
@@ -4586,10 +4622,10 @@
     </row>
     <row r="38" customHeight="1" spans="1:17">
       <c r="A38" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>160</v>
@@ -4598,7 +4634,7 @@
         <v>161</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>22</v>
@@ -4651,7 +4687,7 @@
         <v>165</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>22</v>
@@ -4704,7 +4740,7 @@
         <v>169</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>22</v>
@@ -4721,8 +4757,8 @@
       <c r="J40" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="11" t="s">
-        <v>22</v>
+      <c r="K40" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L40" s="11" t="s">
         <v>22</v>
@@ -4733,11 +4769,11 @@
       <c r="N40" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O40" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P40" s="12" t="s">
-        <v>23</v>
+      <c r="O40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q40" s="17" t="s">
         <v>22</v>
@@ -4757,22 +4793,22 @@
         <v>173</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>23</v>
+        <v>107</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>23</v>
+      <c r="H41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>22</v>
@@ -4780,14 +4816,14 @@
       <c r="L41" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M41" s="12" t="s">
-        <v>23</v>
+      <c r="M41" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="N41" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O41" s="11" t="s">
-        <v>22</v>
+      <c r="O41" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P41" s="12" t="s">
         <v>23</v>
@@ -4810,7 +4846,7 @@
         <v>177</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>23</v>
@@ -4824,8 +4860,8 @@
       <c r="I42" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J42" s="11" t="s">
-        <v>22</v>
+      <c r="J42" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>22</v>
@@ -4842,8 +4878,8 @@
       <c r="O42" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P42" s="11" t="s">
-        <v>22</v>
+      <c r="P42" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="Q42" s="17" t="s">
         <v>22</v>
@@ -4857,13 +4893,13 @@
         <v>179</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>23</v>
@@ -4904,19 +4940,19 @@
     </row>
     <row r="44" customHeight="1" spans="1:17">
       <c r="A44" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>23</v>
@@ -4957,19 +4993,19 @@
     </row>
     <row r="45" customHeight="1" spans="1:17">
       <c r="A45" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>23</v>
@@ -5010,19 +5046,19 @@
     </row>
     <row r="46" customHeight="1" spans="1:17">
       <c r="A46" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>23</v>
@@ -5063,31 +5099,31 @@
     </row>
     <row r="47" customHeight="1" spans="1:17">
       <c r="A47" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>192</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>22</v>
+        <v>107</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="G47" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>22</v>
+      <c r="H47" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>22</v>
@@ -5098,11 +5134,11 @@
       <c r="L47" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N47" s="12" t="s">
-        <v>23</v>
+      <c r="M47" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O47" s="11" t="s">
         <v>22</v>
@@ -5114,7 +5150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" s="16" customFormat="1" customHeight="1" spans="1:17">
+    <row r="48" customHeight="1" spans="1:17">
       <c r="A48" s="2" t="s">
         <v>193</v>
       </c>
@@ -5124,11 +5160,11 @@
       <c r="C48" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="9" t="s">
         <v>196</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>22</v>
@@ -5154,140 +5190,140 @@
       <c r="M48" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O48" s="12" t="s">
-        <v>23</v>
+      <c r="N48" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O48" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="P48" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q48" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="1:17">
-      <c r="A49" s="18" t="s">
+      <c r="Q48" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" s="16" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A49" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="E49" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q49" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:17">
+      <c r="A50" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="F49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="K49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="M49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="O49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="P49" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q49" s="21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="1:17">
-      <c r="A50" s="2" t="s">
+      <c r="B50" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="E50" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q50" s="12" t="s">
+      <c r="E50" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q50" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:17">
       <c r="A51" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>208</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>23</v>
@@ -5327,20 +5363,20 @@
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:17">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D52" s="9" t="s">
+      <c r="C52" s="2" t="s">
         <v>211</v>
       </c>
+      <c r="D52" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="E52" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>23</v>
@@ -5381,19 +5417,19 @@
     </row>
     <row r="53" customHeight="1" spans="1:17">
       <c r="A53" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>215</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>23</v>
@@ -5446,60 +5482,60 @@
         <v>219</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N54" s="11" t="s">
-        <v>22</v>
+        <v>205</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O54" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="P54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q54" s="17" t="s">
-        <v>22</v>
+      <c r="P54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q54" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:17">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="9" t="s">
         <v>223</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>22</v>
@@ -5539,20 +5575,20 @@
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:17">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="2" t="s">
         <v>226</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>227</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>22</v>
@@ -5605,7 +5641,7 @@
         <v>231</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>22</v>
@@ -5658,7 +5694,7 @@
         <v>235</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>22</v>
@@ -5711,7 +5747,7 @@
         <v>239</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>22</v>
@@ -5728,8 +5764,8 @@
       <c r="J59" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K59" s="12" t="s">
-        <v>23</v>
+      <c r="K59" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L59" s="11" t="s">
         <v>22</v>
@@ -5764,7 +5800,7 @@
         <v>243</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>22</v>
@@ -5804,20 +5840,20 @@
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:17">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="9" t="s">
         <v>247</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>22</v>
@@ -5846,8 +5882,8 @@
       <c r="N61" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O61" s="11" t="s">
-        <v>22</v>
+      <c r="O61" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="P61" s="11" t="s">
         <v>22</v>
@@ -5870,7 +5906,7 @@
         <v>251</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>22</v>
@@ -5910,26 +5946,26 @@
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:17">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="D63" s="2" t="s">
         <v>255</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G63" s="12" t="s">
-        <v>23</v>
+      <c r="G63" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="H63" s="11" t="s">
         <v>22</v>
@@ -5937,11 +5973,11 @@
       <c r="I63" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J63" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K63" s="11" t="s">
-        <v>22</v>
+      <c r="J63" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K63" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L63" s="11" t="s">
         <v>22</v>
@@ -5955,11 +5991,11 @@
       <c r="O63" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P63" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q63" s="12" t="s">
-        <v>23</v>
+      <c r="P63" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q63" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:17">
@@ -5976,7 +6012,7 @@
         <v>259</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>22</v>
@@ -6016,26 +6052,26 @@
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:18">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="9" t="s">
         <v>263</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G65" s="11" t="s">
-        <v>22</v>
+      <c r="G65" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H65" s="11" t="s">
         <v>22</v>
@@ -6061,11 +6097,11 @@
       <c r="O65" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P65" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q65" s="17" t="s">
-        <v>22</v>
+      <c r="P65" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q65" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:18">
@@ -6082,7 +6118,7 @@
         <v>267</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>22</v>
@@ -6135,7 +6171,7 @@
         <v>271</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>22</v>
@@ -6188,7 +6224,7 @@
         <v>275</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>22</v>
@@ -6231,7 +6267,7 @@
       <c r="A69" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="2" t="s">
         <v>277</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -6241,7 +6277,7 @@
         <v>279</v>
       </c>
       <c r="E69" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>22</v>
@@ -6284,7 +6320,7 @@
       <c r="A70" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="25" t="s">
         <v>281</v>
       </c>
       <c r="C70" s="2" t="s">
@@ -6294,7 +6330,7 @@
         <v>283</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>22</v>
@@ -6333,7 +6369,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" customFormat="1" customHeight="1" spans="1:18">
+    <row r="71" customHeight="1" spans="1:18">
       <c r="A71" s="2" t="s">
         <v>284</v>
       </c>
@@ -6347,7 +6383,7 @@
         <v>287</v>
       </c>
       <c r="E71" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>22</v>
@@ -6385,9 +6421,8 @@
       <c r="Q71" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="R71" s="2"/>
-    </row>
-    <row r="72" s="16" customFormat="1" customHeight="1" spans="1:18">
+    </row>
+    <row r="72" customFormat="1" customHeight="1" spans="1:18">
       <c r="A72" s="2" t="s">
         <v>288</v>
       </c>
@@ -6401,7 +6436,7 @@
         <v>291</v>
       </c>
       <c r="E72" s="24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>22</v>
@@ -6439,111 +6474,112 @@
       <c r="Q72" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:18">
-      <c r="A73" s="15" t="s">
+      <c r="R72" s="2"/>
+    </row>
+    <row r="73" s="16" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A73" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C73" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D73" s="15" t="s">
+      <c r="C73" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E73" s="26" t="s">
+      <c r="D73" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="F73" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G73" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H73" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I73" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J73" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="K73" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="L73" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="M73" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N73" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="O73" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="P73" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q73" s="22" t="s">
+      <c r="E73" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q73" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:18">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D74" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="E74" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="E74" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="F74" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G74" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H74" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I74" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J74" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K74" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L74" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M74" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N74" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O74" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P74" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q74" s="12" t="s">
-        <v>23</v>
+      <c r="F74" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K74" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L74" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M74" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N74" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O74" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="P74" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q74" s="22" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:18">
@@ -6560,7 +6596,7 @@
         <v>303</v>
       </c>
       <c r="E75" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>22</v>
@@ -6574,8 +6610,8 @@
       <c r="I75" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J75" s="11" t="s">
-        <v>22</v>
+      <c r="J75" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K75" s="11" t="s">
         <v>22</v>
@@ -6586,14 +6622,14 @@
       <c r="M75" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N75" s="11" t="s">
-        <v>22</v>
+      <c r="N75" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="O75" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P75" s="11" t="s">
-        <v>22</v>
+      <c r="P75" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="Q75" s="12" t="s">
         <v>23</v>
@@ -6613,13 +6649,13 @@
         <v>307</v>
       </c>
       <c r="E76" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G76" s="11" t="s">
-        <v>22</v>
+      <c r="G76" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="H76" s="11" t="s">
         <v>22</v>
@@ -6627,14 +6663,14 @@
       <c r="I76" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J76" s="12" t="s">
-        <v>23</v>
+      <c r="J76" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="K76" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L76" s="11" t="s">
-        <v>22</v>
+      <c r="L76" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="M76" s="11" t="s">
         <v>22</v>
@@ -6645,8 +6681,8 @@
       <c r="O76" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P76" s="12" t="s">
-        <v>23</v>
+      <c r="P76" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="Q76" s="12" t="s">
         <v>23</v>
@@ -6666,7 +6702,7 @@
         <v>311</v>
       </c>
       <c r="E77" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>22</v>
@@ -6710,16 +6746,16 @@
         <v>312</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E78" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>22</v>
@@ -6760,19 +6796,19 @@
     </row>
     <row r="79" customHeight="1" spans="1:18">
       <c r="A79" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E79" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F79" s="11" t="s">
         <v>22</v>
@@ -6813,19 +6849,19 @@
     </row>
     <row r="80" customHeight="1" spans="1:18">
       <c r="A80" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>22</v>
@@ -6842,8 +6878,8 @@
       <c r="J80" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K80" s="12" t="s">
-        <v>23</v>
+      <c r="K80" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="L80" s="11" t="s">
         <v>22</v>
@@ -6857,11 +6893,11 @@
       <c r="O80" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P80" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q80" s="17" t="s">
-        <v>22</v>
+      <c r="P80" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q80" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:17">
@@ -6869,16 +6905,16 @@
         <v>321</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F81" s="11" t="s">
         <v>22</v>
@@ -6919,10 +6955,10 @@
     </row>
     <row r="82" customHeight="1" spans="1:17">
       <c r="A82" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>326</v>
@@ -6931,7 +6967,7 @@
         <v>327</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F82" s="11" t="s">
         <v>22</v>
@@ -6984,7 +7020,7 @@
         <v>331</v>
       </c>
       <c r="E83" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F83" s="11" t="s">
         <v>22</v>
@@ -7037,7 +7073,7 @@
         <v>335</v>
       </c>
       <c r="E84" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>22</v>
@@ -7090,7 +7126,7 @@
         <v>339</v>
       </c>
       <c r="E85" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>22</v>
@@ -7107,8 +7143,8 @@
       <c r="J85" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K85" s="11" t="s">
-        <v>22</v>
+      <c r="K85" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L85" s="11" t="s">
         <v>22</v>
@@ -7143,7 +7179,7 @@
         <v>343</v>
       </c>
       <c r="E86" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>22</v>
@@ -7160,8 +7196,8 @@
       <c r="J86" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K86" s="11" t="s">
-        <v>22</v>
+      <c r="K86" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="L86" s="11" t="s">
         <v>22</v>
@@ -7196,7 +7232,7 @@
         <v>347</v>
       </c>
       <c r="E87" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F87" s="11" t="s">
         <v>22</v>
@@ -7243,13 +7279,13 @@
         <v>349</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E88" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>22</v>
@@ -7290,19 +7326,19 @@
     </row>
     <row r="89" customHeight="1" spans="1:17">
       <c r="A89" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E89" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F89" s="11" t="s">
         <v>22</v>
@@ -7334,28 +7370,28 @@
       <c r="O89" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P89" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q89" s="12" t="s">
-        <v>23</v>
+      <c r="P89" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q89" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:17">
       <c r="A90" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>357</v>
+        <v>54</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>358</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>22</v>
@@ -7408,7 +7444,7 @@
         <v>362</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F91" s="11" t="s">
         <v>22</v>
@@ -7440,11 +7476,11 @@
       <c r="O91" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P91" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q91" s="11" t="s">
-        <v>22</v>
+      <c r="P91" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q91" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:17">
@@ -7461,7 +7497,7 @@
         <v>366</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>22</v>
@@ -7496,7 +7532,7 @@
       <c r="P92" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q92" s="11" t="s">
+      <c r="Q92" s="17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -7514,7 +7550,7 @@
         <v>370</v>
       </c>
       <c r="E93" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>22</v>
@@ -7528,8 +7564,8 @@
       <c r="I93" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J93" s="11" t="s">
-        <v>22</v>
+      <c r="J93" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K93" s="11" t="s">
         <v>22</v>
@@ -7546,10 +7582,10 @@
       <c r="O93" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P93" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q93" s="17" t="s">
+      <c r="P93" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q93" s="11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -7567,7 +7603,7 @@
         <v>374</v>
       </c>
       <c r="E94" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>22</v>
@@ -7581,8 +7617,8 @@
       <c r="I94" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J94" s="11" t="s">
-        <v>22</v>
+      <c r="J94" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K94" s="11" t="s">
         <v>22</v>
@@ -7593,8 +7629,8 @@
       <c r="M94" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N94" s="12" t="s">
-        <v>23</v>
+      <c r="N94" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O94" s="11" t="s">
         <v>22</v>
@@ -7602,7 +7638,7 @@
       <c r="P94" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q94" s="17" t="s">
+      <c r="Q94" s="11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -7620,7 +7656,7 @@
         <v>378</v>
       </c>
       <c r="E95" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>22</v>
@@ -7646,44 +7682,153 @@
       <c r="M95" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N95" s="12" t="s">
-        <v>23</v>
+      <c r="N95" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="O95" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P95" s="11" t="s">
-        <v>22</v>
+      <c r="P95" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="Q95" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:17">
+      <c r="A96" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E96" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N96" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P96" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q96" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:17">
+      <c r="A97" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N97" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P97" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q97" s="17" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D31" r:id="rId1" display="https://legacy-docs.dify.ai/zh-hans"/>
+    <hyperlink ref="D32" r:id="rId1" display="https://legacy-docs.dify.ai/zh-hans"/>
     <hyperlink ref="D3" r:id="rId2" display="https://platform.deepseek.com"/>
-    <hyperlink ref="D4" r:id="rId3" display="https://skills.sh" tooltip="https://skills.sh"/>
-    <hyperlink ref="D37" r:id="rId4" display="https://uiverse.io" tooltip="https://uiverse.io"/>
-    <hyperlink ref="D38" r:id="rId5" display="https://inspira-ui.com/docs/cn" tooltip="https://inspira-ui.com/docs/cn"/>
-    <hyperlink ref="D62" r:id="rId6" display="https://color.review" tooltip="https://color.review"/>
-    <hyperlink ref="D39" r:id="rId7" display="https://www.patterns.dev" tooltip="https://www.patterns.dev"/>
-    <hyperlink ref="D67" r:id="rId8" display="https://color.adobe.com/zh"/>
-    <hyperlink ref="D45" r:id="rId9" display="https://std.samr.gov.cn"/>
-    <hyperlink ref="D46" r:id="rId10" display="https://openstd.samr.gov.cn/bzgk/gb/index"/>
-    <hyperlink ref="D44" r:id="rId11" display="https://www.stats.gov.cn"/>
-    <hyperlink ref="D30" r:id="rId12" display="https://tldr.sh"/>
-    <hyperlink ref="D60" r:id="rId13" display="https://chalk.ist"/>
-    <hyperlink ref="D26" r:id="rId14" display="https://nix.dev"/>
-    <hyperlink ref="D32" r:id="rId15" display="https://cn.vuejs.org/guide/introduction.html"/>
-    <hyperlink ref="D33" r:id="rId16" display="https://www.tauri.net.cn/guides"/>
-    <hyperlink ref="D71" r:id="rId17" display="https://colorflow.ls.graphics" tooltip="https://colorflow.ls.graphics"/>
+    <hyperlink ref="D5" r:id="rId3" display="https://skills.sh" tooltip="https://skills.sh"/>
+    <hyperlink ref="D38" r:id="rId4" display="https://uiverse.io" tooltip="https://uiverse.io"/>
+    <hyperlink ref="D39" r:id="rId5" display="https://inspira-ui.com/docs/cn" tooltip="https://inspira-ui.com/docs/cn"/>
+    <hyperlink ref="D63" r:id="rId6" display="https://color.review" tooltip="https://color.review"/>
+    <hyperlink ref="D40" r:id="rId7" display="https://www.patterns.dev" tooltip="https://www.patterns.dev"/>
+    <hyperlink ref="D68" r:id="rId8" display="https://color.adobe.com/zh"/>
+    <hyperlink ref="D46" r:id="rId9" display="https://std.samr.gov.cn"/>
+    <hyperlink ref="D47" r:id="rId10" display="https://openstd.samr.gov.cn/bzgk/gb/index"/>
+    <hyperlink ref="D45" r:id="rId11" display="https://www.stats.gov.cn"/>
+    <hyperlink ref="D31" r:id="rId12" display="https://tldr.sh"/>
+    <hyperlink ref="D61" r:id="rId13" display="https://chalk.ist"/>
+    <hyperlink ref="D27" r:id="rId14" display="https://nix.dev"/>
+    <hyperlink ref="D33" r:id="rId15" display="https://cn.vuejs.org/guide/introduction.html"/>
+    <hyperlink ref="D34" r:id="rId16" display="https://www.tauri.net.cn/guides"/>
+    <hyperlink ref="D72" r:id="rId17" display="https://colorflow.ls.graphics" tooltip="https://colorflow.ls.graphics"/>
+    <hyperlink ref="D4" r:id="rId18" display="https://www.123pan.com" tooltip="https://www.123pan.com"/>
+    <hyperlink ref="D56" r:id="rId19" display="https://www.ipaddress.com"/>
+    <hyperlink ref="D86" r:id="rId20" display="https://xandemon.github.io/developer-icons/icons/All" tooltip="https://xandemon.github.io/developer-icons/icons/All"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="33" orientation="portrait"/>
   <headerFooter/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="106" max="16" man="1"/>
+    <brk id="108" max="16" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="5" max="1048575" man="1"/>
@@ -7694,7 +7839,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" style="2" customWidth="1"/>
@@ -7763,19 +7908,19 @@
     </row>
     <row r="2" customHeight="1" spans="1:17">
       <c r="A2" s="9" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>22</v>
@@ -7816,19 +7961,19 @@
     </row>
     <row r="3" customHeight="1" spans="1:17">
       <c r="A3" s="9" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>22</v>
@@ -7869,19 +8014,19 @@
     </row>
     <row r="4" customHeight="1" spans="1:17">
       <c r="A4" s="9" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D4" s="9">
         <v>2</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>22</v>
@@ -7922,19 +8067,19 @@
     </row>
     <row r="5" customHeight="1" spans="1:17">
       <c r="A5" s="9" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D5" s="9">
         <v>3</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>22</v>
@@ -7975,19 +8120,19 @@
     </row>
     <row r="6" customHeight="1" spans="1:17">
       <c r="A6" s="9" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D6" s="9">
         <v>4</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>22</v>
@@ -8028,19 +8173,19 @@
     </row>
     <row r="7" customHeight="1" spans="1:17">
       <c r="A7" s="9" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D7" s="9">
         <v>5</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>22</v>
@@ -8081,19 +8226,19 @@
     </row>
     <row r="8" customHeight="1" spans="1:17">
       <c r="A8" s="9" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D8" s="9">
         <v>6</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>22</v>
@@ -8134,19 +8279,19 @@
     </row>
     <row r="9" customHeight="1" spans="1:17">
       <c r="A9" s="9" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D9" s="9">
         <v>7</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>22</v>
@@ -8187,19 +8332,19 @@
     </row>
     <row r="10" customHeight="1" spans="1:17">
       <c r="A10" s="9" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D10" s="9">
         <v>8</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>22</v>
@@ -8240,19 +8385,19 @@
     </row>
     <row r="11" customHeight="1" spans="1:17">
       <c r="A11" s="9" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D11" s="9">
         <v>9</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>22</v>
@@ -8293,19 +8438,19 @@
     </row>
     <row r="12" customHeight="1" spans="1:17">
       <c r="A12" s="9" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D12" s="9">
         <v>10</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>22</v>
@@ -8346,19 +8491,19 @@
     </row>
     <row r="13" customHeight="1" spans="1:17">
       <c r="A13" s="9" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D13" s="9">
         <v>11</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>22</v>
@@ -8399,19 +8544,19 @@
     </row>
     <row r="14" customHeight="1" spans="1:17">
       <c r="A14" s="9" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>22</v>
@@ -8452,19 +8597,19 @@
     </row>
     <row r="15" customHeight="1" spans="1:17">
       <c r="A15" s="9" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>22</v>
@@ -8505,19 +8650,19 @@
     </row>
     <row r="16" customHeight="1" spans="1:17">
       <c r="A16" s="9" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>413</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>405</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
@@ -8558,19 +8703,19 @@
     </row>
     <row r="17" customHeight="1" spans="1:17">
       <c r="A17" s="9" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>22</v>
@@ -8611,19 +8756,19 @@
     </row>
     <row r="18" customHeight="1" spans="1:17">
       <c r="A18" s="9" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>22</v>
@@ -8664,19 +8809,19 @@
     </row>
     <row r="19" customHeight="1" spans="1:17">
       <c r="A19" s="9" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>22</v>
@@ -8717,19 +8862,19 @@
     </row>
     <row r="20" customHeight="1" spans="1:17">
       <c r="A20" s="9" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>22</v>
@@ -8770,19 +8915,19 @@
     </row>
     <row r="21" customHeight="1" spans="1:17">
       <c r="A21" s="2" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D21" s="9">
         <v>13</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>22</v>
@@ -8823,19 +8968,19 @@
     </row>
     <row r="22" customHeight="1" spans="1:17">
       <c r="A22" s="9" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>22</v>
@@ -8876,19 +9021,19 @@
     </row>
     <row r="23" customHeight="1" spans="1:17">
       <c r="A23" s="2" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>22</v>
@@ -8929,19 +9074,19 @@
     </row>
     <row r="24" customHeight="1" spans="1:17">
       <c r="A24" s="2" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
@@ -8982,19 +9127,19 @@
     </row>
     <row r="25" customHeight="1" spans="1:17">
       <c r="A25" s="2" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>23</v>
@@ -9034,20 +9179,20 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:17">
-      <c r="A26" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="D26" s="9">
-        <v>15</v>
+      <c r="A26" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>458</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>23</v>
@@ -9088,19 +9233,19 @@
     </row>
     <row r="27" customHeight="1" spans="1:17">
       <c r="A27" s="9" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>453</v>
+        <v>461</v>
+      </c>
+      <c r="D27" s="9">
+        <v>15</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>23</v>
@@ -9141,19 +9286,19 @@
     </row>
     <row r="28" customHeight="1" spans="1:17">
       <c r="A28" s="9" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>23</v>
@@ -9194,19 +9339,19 @@
     </row>
     <row r="29" customHeight="1" spans="1:17">
       <c r="A29" s="9" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>23</v>
@@ -9247,19 +9392,19 @@
     </row>
     <row r="30" customHeight="1" spans="1:17">
       <c r="A30" s="9" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>23</v>
@@ -9300,54 +9445,107 @@
     </row>
     <row r="31" customHeight="1" spans="1:17">
       <c r="A31" s="9" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="D31" s="9">
+        <v>476</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q31" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:17">
+      <c r="A32" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="D32" s="9">
         <v>12</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q31" s="12" t="s">
+      <c r="E32" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q32" s="12" t="s">
         <v>23</v>
       </c>
     </row>
@@ -9357,7 +9555,8 @@
     <hyperlink ref="D16" r:id="rId2" display="http://192.168.31.96:2017"/>
     <hyperlink ref="D18" r:id="rId3" display="http://192.168.31.97:8384"/>
     <hyperlink ref="D20" r:id="rId4" display="http://192.168.31.97:10080/apps"/>
-    <hyperlink ref="D25" r:id="rId5" display="http://192.168.31.97:8222"/>
+    <hyperlink ref="D26" r:id="rId5" display="http://192.168.31.97:8222" tooltip="http://192.168.31.97:8222"/>
+    <hyperlink ref="D25" r:id="rId6" display="http://192.168.31.97:10180" tooltip="http://192.168.31.97:10180"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
